--- a/employees-excel/TAFS_HR_Employee_Intake.xlsx
+++ b/employees-excel/TAFS_HR_Employee_Intake.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="1084">
   <si>
     <t>TAFS — Employee Master Data   |   Fill one row per employee. All fields required unless marked Optional.</t>
   </si>
@@ -2985,6 +2985,468 @@
     <t>HOUSE # 16126, NIPA BRICK IQBAL LINE, FC AREA, CLIFTON CANT, KARACHI</t>
   </si>
   <si>
+    <t>SPORT TEACHER</t>
+  </si>
+  <si>
+    <t>AGHA ABBAS HUSSAIN</t>
+  </si>
+  <si>
+    <t>ALIYA JAHAN</t>
+  </si>
+  <si>
+    <t>C-28, RIZVIA SOCIETY, NAZIMABAD NO. 1, KARACHI</t>
+  </si>
+  <si>
+    <t>06-00572</t>
+  </si>
+  <si>
+    <t>GUARD</t>
+  </si>
+  <si>
+    <t>GHULAM HAIDER</t>
+  </si>
+  <si>
+    <t>WAHID ALI</t>
+  </si>
+  <si>
+    <t>32402-2143723-7</t>
+  </si>
+  <si>
+    <t>06-00573</t>
+  </si>
+  <si>
+    <t>ABID HUSSAIN KHUSA</t>
+  </si>
+  <si>
+    <t>LASHARI LHAN</t>
+  </si>
+  <si>
+    <t>32402-4326444-1</t>
+  </si>
+  <si>
+    <t>06-00564</t>
+  </si>
+  <si>
+    <t>SALEEM ULLAH</t>
+  </si>
+  <si>
+    <t>ABDUL HAMEED</t>
+  </si>
+  <si>
+    <t>45204-2115422-1</t>
+  </si>
+  <si>
+    <t>06-00562</t>
+  </si>
+  <si>
+    <t>ELECTRICIAN</t>
+  </si>
+  <si>
+    <t>ALI HAIDER</t>
+  </si>
+  <si>
+    <t>MUHAMMAD HAROON</t>
+  </si>
+  <si>
+    <t>42201-2567093-9</t>
+  </si>
+  <si>
+    <t>0334-0229433</t>
+  </si>
+  <si>
+    <t>06-00575</t>
+  </si>
+  <si>
+    <t>MUHAMMAD AHMED</t>
+  </si>
+  <si>
+    <t>SANOBER KHAN</t>
+  </si>
+  <si>
+    <t>42201-0260452-1</t>
+  </si>
+  <si>
+    <t>20/05/1989</t>
+  </si>
+  <si>
+    <t>A-175, 2-B LANHI AREA , KARACHI</t>
+  </si>
+  <si>
+    <t>ACADEMIC &amp; ADMINSTRATIVE ASSISTANT</t>
+  </si>
+  <si>
+    <t>MS. SUMMAIYAH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FAROOQ</t>
+  </si>
+  <si>
+    <t>42101-1782249-3</t>
+  </si>
+  <si>
+    <t>B-17, HUNAID CITY, BLOCK # 17, GULISTAN E JOHAR</t>
+  </si>
+  <si>
+    <t>0312-270796</t>
+  </si>
+  <si>
+    <t>02-001481</t>
+  </si>
+  <si>
+    <t>HOME TEACHER KG</t>
+  </si>
+  <si>
+    <t>MS. BENAZIR WASEEM</t>
+  </si>
+  <si>
+    <t>AGHA WASEEM</t>
+  </si>
+  <si>
+    <t>ANILA FATIMA</t>
+  </si>
+  <si>
+    <t>42201-725510-2</t>
+  </si>
+  <si>
+    <t>14-05-2009</t>
+  </si>
+  <si>
+    <t>RIZWA SOCIETY SAFORA CHOWRANGI</t>
+  </si>
+  <si>
+    <t>0315-8958912</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BUI NNN ENGLISH TEACHER JUNIORS</t>
+  </si>
+  <si>
+    <t>MS. AYESHA</t>
+  </si>
+  <si>
+    <t>M. ABDUL SAGHEER</t>
+  </si>
+  <si>
+    <t>SABA</t>
+  </si>
+  <si>
+    <t>42000-1865181-4</t>
+  </si>
+  <si>
+    <t>HOUSE NUMBER C1/15 BLOCK A NORTH NAZIMABAD KARACHI</t>
+  </si>
+  <si>
+    <t>0334-2423481</t>
+  </si>
+  <si>
+    <t>BUI NNN SCIENCE ,ISLAMIYAT URDU</t>
+  </si>
+  <si>
+    <t>MS. MUQADDAS JABIN</t>
+  </si>
+  <si>
+    <t>IRFAN ULLAH</t>
+  </si>
+  <si>
+    <t>ZARNIGAR</t>
+  </si>
+  <si>
+    <t>42101-5322393-4</t>
+  </si>
+  <si>
+    <t>A 15, BLOCK 'I', NEAR KHADIJA MARKET, NORTH NAZIMABAD</t>
+  </si>
+  <si>
+    <t>0330-2490796</t>
+  </si>
+  <si>
+    <t>BUI NNN HOME TEACHER (JR. II)</t>
+  </si>
+  <si>
+    <t>MS. FOZIA NIGHAT</t>
+  </si>
+  <si>
+    <t>ARIF QAMAR ALVI</t>
+  </si>
+  <si>
+    <t>PERVEN</t>
+  </si>
+  <si>
+    <t>42101-1700605-4</t>
+  </si>
+  <si>
+    <t>FLAT # B-15, BLESSING PLAZA, BLOCK - K, NORTH NAZIMABAD</t>
+  </si>
+  <si>
+    <t>0334-3178172</t>
+  </si>
+  <si>
+    <t>BUI NNN HOME TEACHER (JR. I)</t>
+  </si>
+  <si>
+    <t>MS. MEHAK MUBASHIRA</t>
+  </si>
+  <si>
+    <t>MUBASHIR AHMED KHALID</t>
+  </si>
+  <si>
+    <t>ABIDA NASEEM</t>
+  </si>
+  <si>
+    <t>42101-8761589-6</t>
+  </si>
+  <si>
+    <t>R-283 BLOCK15 FB AREA</t>
+  </si>
+  <si>
+    <t>0319-8364843</t>
+  </si>
+  <si>
+    <t>BUI NNN HOME TEACHER (PRE-NUR AND NUR)</t>
+  </si>
+  <si>
+    <t>MS. AIMAN IMRAN</t>
+  </si>
+  <si>
+    <t>M. IMRAN</t>
+  </si>
+  <si>
+    <t>NOSHEEN</t>
+  </si>
+  <si>
+    <t>42101-5919341-4</t>
+  </si>
+  <si>
+    <t>HOUSE # 156, SECTOR 3, NORTH KARACHI</t>
+  </si>
+  <si>
+    <t>0312-2028706</t>
+  </si>
+  <si>
+    <t>BUI NNN MATHS JR. III - V ,SOCIAL STUDIES , URDU</t>
+  </si>
+  <si>
+    <t>MS. JAVAIRA SHAHZAD</t>
+  </si>
+  <si>
+    <t>SYED TALIB NAUMAN</t>
+  </si>
+  <si>
+    <t>NEELOFER TALIB</t>
+  </si>
+  <si>
+    <t>42101-1332520-2</t>
+  </si>
+  <si>
+    <t>FLAT # 204, AERO CLOCK TOWER, BL-L, NORTH NAZIMABAD</t>
+  </si>
+  <si>
+    <t>0321-3686001</t>
+  </si>
+  <si>
+    <t>BUI NNN HOME TEACHER KG.</t>
+  </si>
+  <si>
+    <t>MS. SAMREEN IRFAN</t>
+  </si>
+  <si>
+    <t>RANA BASHIR</t>
+  </si>
+  <si>
+    <t>HAFIZA BANO</t>
+  </si>
+  <si>
+    <t>42101-1700297-6</t>
+  </si>
+  <si>
+    <t>HOUSE # 11 A5-E, MAIN M. SIDDIIQ BUILDING, PAPOSH</t>
+  </si>
+  <si>
+    <t>0335-3248221</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00019</t>
+  </si>
+  <si>
+    <t>GKF HOME TEACHER P.N</t>
+  </si>
+  <si>
+    <t>MS.SYEDA RUBAB NAQVI</t>
+  </si>
+  <si>
+    <t>SYED MUJAHID HUSSAIN NAQVI</t>
+  </si>
+  <si>
+    <t>SHAISTA PARVEEN</t>
+  </si>
+  <si>
+    <t>42201-5184279-8</t>
+  </si>
+  <si>
+    <t>Hno L1801 block 1 kaniz Fatima society Gulzar e hijri scheme 33 Karachi</t>
+  </si>
+  <si>
+    <t>0321-3389700</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00010</t>
+  </si>
+  <si>
+    <t>SEPT 01, 2025</t>
+  </si>
+  <si>
+    <t>GKF CO-TEACHER</t>
+  </si>
+  <si>
+    <t>MS. ALISHBA AHMED</t>
+  </si>
+  <si>
+    <t>SAEED AHMED</t>
+  </si>
+  <si>
+    <t>SADIA SAEED</t>
+  </si>
+  <si>
+    <t>42501-6670452-8</t>
+  </si>
+  <si>
+    <t>D-75, RUFI SPRING FLOWER, G-E-H, SCHEME 33</t>
+  </si>
+  <si>
+    <t>0332-2341721</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00011</t>
+  </si>
+  <si>
+    <t>SEPT 15, 2025</t>
+  </si>
+  <si>
+    <t>GKF HOME TEACHER KG.</t>
+  </si>
+  <si>
+    <t>MS. AMBREEN UZAIR</t>
+  </si>
+  <si>
+    <t>ABDUL RASHID</t>
+  </si>
+  <si>
+    <t>ANJUM PERVEEN</t>
+  </si>
+  <si>
+    <t>42101-0544039-6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>B-5, KANEEZ FATIMA SOCIETY, BL - 2</t>
+  </si>
+  <si>
+    <t>0306-2175766</t>
+  </si>
+  <si>
+    <t>02-00020</t>
+  </si>
+  <si>
+    <t>MS.ASBAH BATOOL</t>
+  </si>
+  <si>
+    <t>BAKHTIAR AHMED</t>
+  </si>
+  <si>
+    <t>UZMA BAKHTIAR</t>
+  </si>
+  <si>
+    <t>42201-69756388</t>
+  </si>
+  <si>
+    <t>KANEEZ FATIMA SOCIETY, BL - 01</t>
+  </si>
+  <si>
+    <t>0336-2357511</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00014</t>
+  </si>
+  <si>
+    <t>SEPT 19, 2025</t>
+  </si>
+  <si>
+    <t>GKF JUNIOR TEACHER</t>
+  </si>
+  <si>
+    <t>MS. HUSNIA RAHEEM</t>
+  </si>
+  <si>
+    <t>ABDUL RAHEEM</t>
+  </si>
+  <si>
+    <t>ZARMINE</t>
+  </si>
+  <si>
+    <t>42201-9103653-2</t>
+  </si>
+  <si>
+    <t>MALIK CO-OPERATION SOCIETY</t>
+  </si>
+  <si>
+    <t>0334-3199480</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00015</t>
+  </si>
+  <si>
+    <t>GKF JUNIOR'S SCIENCE TEACHER</t>
+  </si>
+  <si>
+    <t>MS. SANA BATOOL</t>
+  </si>
+  <si>
+    <t>42201-0912719-4</t>
+  </si>
+  <si>
+    <t>24 ARIL2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02-00018</t>
+  </si>
+  <si>
+    <t>MS. ATIQA SAEED</t>
+  </si>
+  <si>
+    <t>SAEED ALI</t>
+  </si>
+  <si>
+    <t>ZOHRA SAEED</t>
+  </si>
+  <si>
+    <t>71703-0569502-0</t>
+  </si>
+  <si>
+    <t>AWAN-E-LIAQUAT GIRLS HOSTEL, UNIVERSITY OF KARACHI (KU)</t>
+  </si>
+  <si>
+    <t>0355-5364328</t>
+  </si>
+  <si>
+    <t>04-0050118</t>
+  </si>
+  <si>
+    <t>MAID HOME</t>
+  </si>
+  <si>
+    <t>04-005051</t>
+  </si>
+  <si>
+    <t>TASLEEEM</t>
+  </si>
+  <si>
+    <t>04-005062</t>
+  </si>
+  <si>
+    <t>AZRA RIAZ</t>
+  </si>
+  <si>
     <t>TAFS — Attendance &amp; Pay Settings   |   One row per employee. Employee Code must match Sheet 1. Reporting/Leaving time in HH:MM (24-hr). Late relaxation in minutes (e.g. 5). Monthly pay in PKR (whole number). Staff type: domestic / old_admin / new_admin / teacher. Campus: Johar / Kaneez Fatima / North Nazimabad. Class-Section format: 6:A,B;7:A,C  (class:sections;class:sections)</t>
   </si>
   <si>
@@ -3233,7 +3695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="9">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="mm-yyyy"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
@@ -3243,8 +3705,12 @@
     <numFmt numFmtId="170" formatCode="d mmmm yyyy"/>
     <numFmt numFmtId="171" formatCode="dd-mmm-yy"/>
     <numFmt numFmtId="172" formatCode="m-d-yyyy"/>
+    <numFmt numFmtId="173" formatCode="mmm d, yyyy"/>
+    <numFmt numFmtId="174" formatCode="mmm dd, yyyy"/>
+    <numFmt numFmtId="175" formatCode="d-mmmm-yy"/>
+    <numFmt numFmtId="176" formatCode="d-mmm-yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -3327,6 +3793,26 @@
       <name val="&quot;Times New Roman&quot;"/>
     </font>
     <font>
+      <sz val="7.0"/>
+      <color theme="1"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
+      <sz val="7.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color theme="1"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -3375,7 +3861,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border/>
     <border>
       <left style="thin">
@@ -3419,6 +3905,11 @@
       </right>
     </border>
     <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -3444,7 +3935,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="130">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3656,37 +4147,121 @@
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="173" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="11" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="15" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="16" numFmtId="174" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="17" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="17" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="16" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="16" numFmtId="173" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="16" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="18" numFmtId="171" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="18" numFmtId="175" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="18" numFmtId="176" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="18" numFmtId="173" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="14" numFmtId="173" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="174" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="173" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="21" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3695,13 +4270,13 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3716,29 +4291,32 @@
     <xf borderId="1" fillId="0" fontId="0" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="17" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="21" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="20" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="19" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="23" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -7694,29 +8272,61 @@
       <c r="N105" s="48"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="48"/>
-      <c r="B106" s="48"/>
-      <c r="C106" s="48"/>
-      <c r="D106" s="48"/>
-      <c r="E106" s="48"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="48"/>
-      <c r="H106" s="48"/>
-      <c r="I106" s="48"/>
-      <c r="J106" s="48"/>
-      <c r="K106" s="48"/>
+      <c r="A106" s="38" t="s">
+        <v>525</v>
+      </c>
+      <c r="B106" s="37">
+        <v>42415.0</v>
+      </c>
+      <c r="C106" s="60" t="s">
+        <v>853</v>
+      </c>
+      <c r="D106" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="E106" s="38" t="s">
+        <v>854</v>
+      </c>
+      <c r="F106" s="38" t="s">
+        <v>855</v>
+      </c>
+      <c r="G106" s="38" t="s">
+        <v>490</v>
+      </c>
+      <c r="H106" s="71">
+        <v>23235.0</v>
+      </c>
+      <c r="I106" s="38" t="s">
+        <v>856</v>
+      </c>
+      <c r="J106" s="38" t="s">
+        <v>531</v>
+      </c>
+      <c r="K106" s="38"/>
       <c r="L106" s="48"/>
       <c r="M106" s="48"/>
       <c r="N106" s="48"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="48"/>
-      <c r="B107" s="48"/>
-      <c r="C107" s="48"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="48"/>
+      <c r="A107" s="60" t="s">
+        <v>857</v>
+      </c>
+      <c r="B107" s="72">
+        <v>46084.0</v>
+      </c>
+      <c r="C107" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="D107" s="60" t="s">
+        <v>859</v>
+      </c>
+      <c r="E107" s="60" t="s">
+        <v>860</v>
+      </c>
       <c r="F107" s="48"/>
-      <c r="G107" s="48"/>
+      <c r="G107" s="60" t="s">
+        <v>861</v>
+      </c>
       <c r="H107" s="48"/>
       <c r="I107" s="48"/>
       <c r="J107" s="48"/>
@@ -7726,13 +8336,25 @@
       <c r="N107" s="48"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="48"/>
-      <c r="B108" s="48"/>
-      <c r="C108" s="48"/>
-      <c r="D108" s="48"/>
-      <c r="E108" s="48"/>
+      <c r="A108" s="60" t="s">
+        <v>862</v>
+      </c>
+      <c r="B108" s="61">
+        <v>46109.0</v>
+      </c>
+      <c r="C108" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="D108" s="60" t="s">
+        <v>863</v>
+      </c>
+      <c r="E108" s="60" t="s">
+        <v>864</v>
+      </c>
       <c r="F108" s="48"/>
-      <c r="G108" s="48"/>
+      <c r="G108" s="60" t="s">
+        <v>865</v>
+      </c>
       <c r="H108" s="48"/>
       <c r="I108" s="48"/>
       <c r="J108" s="48"/>
@@ -7742,13 +8364,25 @@
       <c r="N108" s="48"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="48"/>
-      <c r="B109" s="48"/>
-      <c r="C109" s="48"/>
-      <c r="D109" s="48"/>
-      <c r="E109" s="48"/>
+      <c r="A109" s="60" t="s">
+        <v>866</v>
+      </c>
+      <c r="B109" s="61">
+        <v>45669.0</v>
+      </c>
+      <c r="C109" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="D109" s="60" t="s">
+        <v>867</v>
+      </c>
+      <c r="E109" s="60" t="s">
+        <v>868</v>
+      </c>
       <c r="F109" s="48"/>
-      <c r="G109" s="48"/>
+      <c r="G109" s="60" t="s">
+        <v>869</v>
+      </c>
       <c r="H109" s="48"/>
       <c r="I109" s="48"/>
       <c r="J109" s="48"/>
@@ -7758,31 +8392,61 @@
       <c r="N109" s="48"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="48"/>
-      <c r="B110" s="48"/>
-      <c r="C110" s="48"/>
-      <c r="D110" s="48"/>
-      <c r="E110" s="48"/>
+      <c r="A110" s="60" t="s">
+        <v>870</v>
+      </c>
+      <c r="B110" s="73">
+        <v>45971.0</v>
+      </c>
+      <c r="C110" s="60" t="s">
+        <v>871</v>
+      </c>
+      <c r="D110" s="60" t="s">
+        <v>872</v>
+      </c>
+      <c r="E110" s="60" t="s">
+        <v>873</v>
+      </c>
       <c r="F110" s="48"/>
-      <c r="G110" s="48"/>
+      <c r="G110" s="60" t="s">
+        <v>874</v>
+      </c>
       <c r="H110" s="48"/>
       <c r="I110" s="48"/>
-      <c r="J110" s="48"/>
+      <c r="J110" s="60" t="s">
+        <v>875</v>
+      </c>
       <c r="K110" s="48"/>
       <c r="L110" s="48"/>
       <c r="M110" s="48"/>
       <c r="N110" s="48"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="48"/>
-      <c r="B111" s="48"/>
-      <c r="C111" s="48"/>
-      <c r="D111" s="48"/>
-      <c r="E111" s="48"/>
+      <c r="A111" s="60" t="s">
+        <v>876</v>
+      </c>
+      <c r="B111" s="72">
+        <v>46210.0</v>
+      </c>
+      <c r="C111" s="60" t="s">
+        <v>871</v>
+      </c>
+      <c r="D111" s="60" t="s">
+        <v>877</v>
+      </c>
+      <c r="E111" s="60" t="s">
+        <v>878</v>
+      </c>
       <c r="F111" s="48"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="48"/>
-      <c r="I111" s="48"/>
+      <c r="G111" s="60" t="s">
+        <v>879</v>
+      </c>
+      <c r="H111" s="60" t="s">
+        <v>880</v>
+      </c>
+      <c r="I111" s="60" t="s">
+        <v>881</v>
+      </c>
       <c r="J111" s="48"/>
       <c r="K111" s="48"/>
       <c r="L111" s="48"/>
@@ -7790,69 +8454,679 @@
       <c r="N111" s="48"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="48"/>
-      <c r="B112" s="48"/>
-      <c r="C112" s="48"/>
-      <c r="D112" s="48"/>
-      <c r="E112" s="48"/>
-      <c r="F112" s="48"/>
-      <c r="G112" s="48"/>
-      <c r="H112" s="48"/>
-      <c r="I112" s="48"/>
-      <c r="J112" s="48"/>
+      <c r="A112" s="74" t="s">
+        <v>500</v>
+      </c>
+      <c r="B112" s="61">
+        <v>46216.0</v>
+      </c>
+      <c r="C112" s="60" t="s">
+        <v>882</v>
+      </c>
+      <c r="D112" s="75" t="s">
+        <v>883</v>
+      </c>
+      <c r="E112" s="76" t="s">
+        <v>884</v>
+      </c>
+      <c r="F112" s="76" t="s">
+        <v>437</v>
+      </c>
+      <c r="G112" s="74" t="s">
+        <v>885</v>
+      </c>
+      <c r="H112" s="77">
+        <v>38113.0</v>
+      </c>
+      <c r="I112" s="76" t="s">
+        <v>886</v>
+      </c>
+      <c r="J112" s="74" t="s">
+        <v>887</v>
+      </c>
       <c r="K112" s="48"/>
       <c r="L112" s="48"/>
       <c r="M112" s="48"/>
       <c r="N112" s="48"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="48"/>
-      <c r="B113" s="48"/>
-      <c r="C113" s="48"/>
-      <c r="D113" s="48"/>
-      <c r="E113" s="48"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="48"/>
-      <c r="H113" s="48"/>
-      <c r="I113" s="48"/>
-      <c r="J113" s="48"/>
+      <c r="A113" s="60" t="s">
+        <v>888</v>
+      </c>
+      <c r="B113" s="61">
+        <v>46218.0</v>
+      </c>
+      <c r="C113" s="60" t="s">
+        <v>889</v>
+      </c>
+      <c r="D113" s="60" t="s">
+        <v>890</v>
+      </c>
+      <c r="E113" s="60" t="s">
+        <v>891</v>
+      </c>
+      <c r="F113" s="60" t="s">
+        <v>892</v>
+      </c>
+      <c r="G113" s="60" t="s">
+        <v>893</v>
+      </c>
+      <c r="H113" s="60" t="s">
+        <v>894</v>
+      </c>
+      <c r="I113" s="60" t="s">
+        <v>895</v>
+      </c>
+      <c r="J113" s="60" t="s">
+        <v>896</v>
+      </c>
       <c r="K113" s="48"/>
       <c r="L113" s="48"/>
       <c r="M113" s="48"/>
       <c r="N113" s="48"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="48"/>
-      <c r="B114" s="48"/>
-      <c r="C114" s="48"/>
-      <c r="D114" s="48"/>
-      <c r="E114" s="48"/>
-      <c r="F114" s="48"/>
-      <c r="G114" s="48"/>
-      <c r="H114" s="48"/>
-      <c r="I114" s="48"/>
-      <c r="J114" s="48"/>
+      <c r="A114" s="78">
+        <v>14642.0</v>
+      </c>
+      <c r="B114" s="79">
+        <v>45201.0</v>
+      </c>
+      <c r="C114" s="80" t="s">
+        <v>897</v>
+      </c>
+      <c r="D114" s="81" t="s">
+        <v>898</v>
+      </c>
+      <c r="E114" s="80" t="s">
+        <v>899</v>
+      </c>
+      <c r="F114" s="80" t="s">
+        <v>900</v>
+      </c>
+      <c r="G114" s="82" t="s">
+        <v>901</v>
+      </c>
+      <c r="H114" s="83">
+        <v>37574.0</v>
+      </c>
+      <c r="I114" s="82" t="s">
+        <v>902</v>
+      </c>
+      <c r="J114" s="80" t="s">
+        <v>903</v>
+      </c>
       <c r="K114" s="48"/>
       <c r="L114" s="48"/>
       <c r="M114" s="48"/>
       <c r="N114" s="48"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
+      <c r="O114" s="55"/>
+      <c r="P114" s="55"/>
+      <c r="Q114" s="55"/>
+      <c r="R114" s="55"/>
+      <c r="S114" s="55"/>
+      <c r="T114" s="55"/>
+      <c r="U114" s="55"/>
+      <c r="V114" s="55"/>
+      <c r="W114" s="55"/>
+      <c r="X114" s="55"/>
+      <c r="Y114" s="55"/>
+      <c r="Z114" s="55"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="78">
+        <v>19391.0</v>
+      </c>
+      <c r="B115" s="84">
+        <v>45334.0</v>
+      </c>
+      <c r="C115" s="80" t="s">
+        <v>904</v>
+      </c>
+      <c r="D115" s="81" t="s">
+        <v>905</v>
+      </c>
+      <c r="E115" s="80" t="s">
+        <v>906</v>
+      </c>
+      <c r="F115" s="80" t="s">
+        <v>907</v>
+      </c>
+      <c r="G115" s="82" t="s">
+        <v>908</v>
+      </c>
+      <c r="H115" s="85">
+        <v>36350.0</v>
+      </c>
+      <c r="I115" s="82" t="s">
+        <v>909</v>
+      </c>
+      <c r="J115" s="80" t="s">
+        <v>910</v>
+      </c>
+      <c r="K115" s="55"/>
+      <c r="L115" s="55"/>
+      <c r="M115" s="55"/>
+      <c r="N115" s="55"/>
+      <c r="O115" s="55"/>
+      <c r="P115" s="55"/>
+      <c r="Q115" s="55"/>
+      <c r="R115" s="55"/>
+      <c r="S115" s="55"/>
+      <c r="T115" s="55"/>
+      <c r="U115" s="55"/>
+      <c r="V115" s="55"/>
+      <c r="W115" s="55"/>
+      <c r="X115" s="55"/>
+      <c r="Y115" s="55"/>
+      <c r="Z115" s="55"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="78">
+        <v>20121.0</v>
+      </c>
+      <c r="B116" s="84">
+        <v>45339.0</v>
+      </c>
+      <c r="C116" s="80" t="s">
+        <v>911</v>
+      </c>
+      <c r="D116" s="81" t="s">
+        <v>912</v>
+      </c>
+      <c r="E116" s="80" t="s">
+        <v>913</v>
+      </c>
+      <c r="F116" s="80" t="s">
+        <v>914</v>
+      </c>
+      <c r="G116" s="82" t="s">
+        <v>915</v>
+      </c>
+      <c r="H116" s="84">
+        <v>30004.0</v>
+      </c>
+      <c r="I116" s="82" t="s">
+        <v>916</v>
+      </c>
+      <c r="J116" s="80" t="s">
+        <v>917</v>
+      </c>
+      <c r="K116" s="55"/>
+      <c r="L116" s="55"/>
+      <c r="M116" s="55"/>
+      <c r="N116" s="55"/>
+      <c r="O116" s="55"/>
+      <c r="P116" s="55"/>
+      <c r="Q116" s="55"/>
+      <c r="R116" s="55"/>
+      <c r="S116" s="55"/>
+      <c r="T116" s="55"/>
+      <c r="U116" s="55"/>
+      <c r="V116" s="55"/>
+      <c r="W116" s="55"/>
+      <c r="X116" s="55"/>
+      <c r="Y116" s="55"/>
+      <c r="Z116" s="55"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="78">
+        <v>24139.0</v>
+      </c>
+      <c r="B117" s="79">
+        <v>45600.0</v>
+      </c>
+      <c r="C117" s="80" t="s">
+        <v>918</v>
+      </c>
+      <c r="D117" s="81" t="s">
+        <v>919</v>
+      </c>
+      <c r="E117" s="80" t="s">
+        <v>920</v>
+      </c>
+      <c r="F117" s="80" t="s">
+        <v>921</v>
+      </c>
+      <c r="G117" s="82" t="s">
+        <v>922</v>
+      </c>
+      <c r="H117" s="84">
+        <v>38031.0</v>
+      </c>
+      <c r="I117" s="82" t="s">
+        <v>923</v>
+      </c>
+      <c r="J117" s="80" t="s">
+        <v>924</v>
+      </c>
+      <c r="K117" s="55"/>
+      <c r="L117" s="55"/>
+      <c r="M117" s="55"/>
+      <c r="N117" s="55"/>
+      <c r="O117" s="55"/>
+      <c r="P117" s="55"/>
+      <c r="Q117" s="55"/>
+      <c r="R117" s="55"/>
+      <c r="S117" s="55"/>
+      <c r="T117" s="55"/>
+      <c r="U117" s="55"/>
+      <c r="V117" s="55"/>
+      <c r="W117" s="55"/>
+      <c r="X117" s="55"/>
+      <c r="Y117" s="55"/>
+      <c r="Z117" s="55"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="78">
+        <v>24504.0</v>
+      </c>
+      <c r="B118" s="84">
+        <v>45617.0</v>
+      </c>
+      <c r="C118" s="80" t="s">
+        <v>925</v>
+      </c>
+      <c r="D118" s="81" t="s">
+        <v>926</v>
+      </c>
+      <c r="E118" s="80" t="s">
+        <v>927</v>
+      </c>
+      <c r="F118" s="80" t="s">
+        <v>928</v>
+      </c>
+      <c r="G118" s="82" t="s">
+        <v>929</v>
+      </c>
+      <c r="H118" s="79">
+        <v>37630.0</v>
+      </c>
+      <c r="I118" s="82" t="s">
+        <v>930</v>
+      </c>
+      <c r="J118" s="80" t="s">
+        <v>931</v>
+      </c>
+      <c r="K118" s="55"/>
+      <c r="L118" s="55"/>
+      <c r="M118" s="55"/>
+      <c r="N118" s="55"/>
+      <c r="O118" s="55"/>
+      <c r="P118" s="55"/>
+      <c r="Q118" s="55"/>
+      <c r="R118" s="55"/>
+      <c r="S118" s="55"/>
+      <c r="T118" s="55"/>
+      <c r="U118" s="55"/>
+      <c r="V118" s="55"/>
+      <c r="W118" s="55"/>
+      <c r="X118" s="55"/>
+      <c r="Y118" s="55"/>
+      <c r="Z118" s="55"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="78">
+        <v>25600.0</v>
+      </c>
+      <c r="B119" s="84">
+        <v>45897.0</v>
+      </c>
+      <c r="C119" s="80" t="s">
+        <v>932</v>
+      </c>
+      <c r="D119" s="81" t="s">
+        <v>933</v>
+      </c>
+      <c r="E119" s="80" t="s">
+        <v>934</v>
+      </c>
+      <c r="F119" s="80" t="s">
+        <v>935</v>
+      </c>
+      <c r="G119" s="82" t="s">
+        <v>936</v>
+      </c>
+      <c r="H119" s="83">
+        <v>30030.0</v>
+      </c>
+      <c r="I119" s="82" t="s">
+        <v>937</v>
+      </c>
+      <c r="J119" s="80" t="s">
+        <v>938</v>
+      </c>
+      <c r="K119" s="55"/>
+      <c r="L119" s="55"/>
+      <c r="M119" s="55"/>
+      <c r="N119" s="55"/>
+      <c r="O119" s="55"/>
+      <c r="P119" s="55"/>
+      <c r="Q119" s="55"/>
+      <c r="R119" s="55"/>
+      <c r="S119" s="55"/>
+      <c r="T119" s="55"/>
+      <c r="U119" s="55"/>
+      <c r="V119" s="55"/>
+      <c r="W119" s="55"/>
+      <c r="X119" s="55"/>
+      <c r="Y119" s="55"/>
+      <c r="Z119" s="55"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="78">
+        <v>25965.0</v>
+      </c>
+      <c r="B120" s="84">
+        <v>45898.0</v>
+      </c>
+      <c r="C120" s="80" t="s">
+        <v>939</v>
+      </c>
+      <c r="D120" s="81" t="s">
+        <v>940</v>
+      </c>
+      <c r="E120" s="80" t="s">
+        <v>941</v>
+      </c>
+      <c r="F120" s="80" t="s">
+        <v>942</v>
+      </c>
+      <c r="G120" s="82" t="s">
+        <v>943</v>
+      </c>
+      <c r="H120" s="84">
+        <v>30296.0</v>
+      </c>
+      <c r="I120" s="82" t="s">
+        <v>944</v>
+      </c>
+      <c r="J120" s="80" t="s">
+        <v>945</v>
+      </c>
+      <c r="K120" s="55"/>
+      <c r="L120" s="55"/>
+      <c r="M120" s="55"/>
+      <c r="N120" s="55"/>
+      <c r="O120" s="55"/>
+      <c r="P120" s="55"/>
+      <c r="Q120" s="55"/>
+      <c r="R120" s="55"/>
+      <c r="S120" s="55"/>
+      <c r="T120" s="55"/>
+      <c r="U120" s="55"/>
+      <c r="V120" s="55"/>
+      <c r="W120" s="55"/>
+      <c r="X120" s="55"/>
+      <c r="Y120" s="55"/>
+      <c r="Z120" s="55"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="86" t="s">
+        <v>946</v>
+      </c>
+      <c r="B121" s="87">
+        <v>46027.0</v>
+      </c>
+      <c r="C121" s="86" t="s">
+        <v>947</v>
+      </c>
+      <c r="D121" s="86" t="s">
+        <v>948</v>
+      </c>
+      <c r="E121" s="86" t="s">
+        <v>949</v>
+      </c>
+      <c r="F121" s="86" t="s">
+        <v>950</v>
+      </c>
+      <c r="G121" s="86" t="s">
+        <v>951</v>
+      </c>
+      <c r="H121" s="87">
+        <v>32363.0</v>
+      </c>
+      <c r="I121" s="86" t="s">
+        <v>952</v>
+      </c>
+      <c r="J121" s="86" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="86" t="s">
+        <v>954</v>
+      </c>
+      <c r="B122" s="86" t="s">
+        <v>955</v>
+      </c>
+      <c r="C122" s="86" t="s">
+        <v>956</v>
+      </c>
+      <c r="D122" s="86" t="s">
+        <v>957</v>
+      </c>
+      <c r="E122" s="86" t="s">
+        <v>958</v>
+      </c>
+      <c r="F122" s="86" t="s">
+        <v>959</v>
+      </c>
+      <c r="G122" s="86" t="s">
+        <v>960</v>
+      </c>
+      <c r="H122" s="88">
+        <v>37764.0</v>
+      </c>
+      <c r="I122" s="86" t="s">
+        <v>961</v>
+      </c>
+      <c r="J122" s="86" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="86" t="s">
+        <v>963</v>
+      </c>
+      <c r="B123" s="86" t="s">
+        <v>964</v>
+      </c>
+      <c r="C123" s="86" t="s">
+        <v>965</v>
+      </c>
+      <c r="D123" s="86" t="s">
+        <v>966</v>
+      </c>
+      <c r="E123" s="86" t="s">
+        <v>967</v>
+      </c>
+      <c r="F123" s="86" t="s">
+        <v>968</v>
+      </c>
+      <c r="G123" s="86" t="s">
+        <v>969</v>
+      </c>
+      <c r="H123" s="86" t="s">
+        <v>970</v>
+      </c>
+      <c r="I123" s="86" t="s">
+        <v>971</v>
+      </c>
+      <c r="J123" s="86" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="86" t="s">
+        <v>973</v>
+      </c>
+      <c r="B124" s="89">
+        <v>38683.0</v>
+      </c>
+      <c r="C124" s="86" t="s">
+        <v>956</v>
+      </c>
+      <c r="D124" s="86" t="s">
+        <v>974</v>
+      </c>
+      <c r="E124" s="86" t="s">
+        <v>975</v>
+      </c>
+      <c r="F124" s="86" t="s">
+        <v>976</v>
+      </c>
+      <c r="G124" s="86" t="s">
+        <v>977</v>
+      </c>
+      <c r="H124" s="87">
+        <v>46030.0</v>
+      </c>
+      <c r="I124" s="86" t="s">
+        <v>978</v>
+      </c>
+      <c r="J124" s="86" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="86" t="s">
+        <v>980</v>
+      </c>
+      <c r="B125" s="86" t="s">
+        <v>981</v>
+      </c>
+      <c r="C125" s="86" t="s">
+        <v>982</v>
+      </c>
+      <c r="D125" s="86" t="s">
+        <v>983</v>
+      </c>
+      <c r="E125" s="86" t="s">
+        <v>984</v>
+      </c>
+      <c r="F125" s="86" t="s">
+        <v>985</v>
+      </c>
+      <c r="G125" s="86" t="s">
+        <v>986</v>
+      </c>
+      <c r="H125" s="89">
+        <v>34531.0</v>
+      </c>
+      <c r="I125" s="86" t="s">
+        <v>987</v>
+      </c>
+      <c r="J125" s="86" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="86" t="s">
+        <v>989</v>
+      </c>
+      <c r="B126" s="90">
+        <v>45946.0</v>
+      </c>
+      <c r="C126" s="86" t="s">
+        <v>990</v>
+      </c>
+      <c r="D126" s="86" t="s">
+        <v>991</v>
+      </c>
+      <c r="E126" s="86" t="s">
+        <v>975</v>
+      </c>
+      <c r="F126" s="86" t="s">
+        <v>976</v>
+      </c>
+      <c r="G126" s="86" t="s">
+        <v>992</v>
+      </c>
+      <c r="H126" s="86" t="s">
+        <v>993</v>
+      </c>
+      <c r="I126" s="86" t="s">
+        <v>978</v>
+      </c>
+      <c r="J126" s="86" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="86" t="s">
+        <v>994</v>
+      </c>
+      <c r="B127" s="90">
+        <v>45960.0</v>
+      </c>
+      <c r="C127" s="86" t="s">
+        <v>982</v>
+      </c>
+      <c r="D127" s="86" t="s">
+        <v>995</v>
+      </c>
+      <c r="E127" s="86" t="s">
+        <v>996</v>
+      </c>
+      <c r="F127" s="86" t="s">
+        <v>997</v>
+      </c>
+      <c r="G127" s="86" t="s">
+        <v>998</v>
+      </c>
+      <c r="H127" s="89">
+        <v>37493.0</v>
+      </c>
+      <c r="I127" s="86" t="s">
+        <v>999</v>
+      </c>
+      <c r="J127" s="86" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="67" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B128" s="91">
+        <v>44589.0</v>
+      </c>
+      <c r="C128" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D128" s="93" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="94" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B129" s="95">
+        <v>45597.0</v>
+      </c>
+      <c r="C129" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D129" s="94" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="96" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B130" s="97">
+        <v>45684.0</v>
+      </c>
+      <c r="C130" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D130" s="98" t="s">
+        <v>1006</v>
+      </c>
+    </row>
     <row r="131" ht="15.75" customHeight="1"/>
     <row r="132" ht="15.75" customHeight="1"/>
     <row r="133" ht="15.75" customHeight="1"/>
@@ -8697,7 +9971,6 @@
     <row r="972" ht="15.75" customHeight="1"/>
     <row r="973" ht="15.75" customHeight="1"/>
     <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
@@ -8788,70 +10061,70 @@
   <sheetData>
     <row r="1" ht="51.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>853</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="2" ht="60.0" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>854</v>
+        <v>1008</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>855</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>856</v>
+        <v>1010</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>857</v>
+        <v>1011</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>858</v>
+        <v>1012</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>859</v>
+        <v>1013</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>860</v>
+        <v>1014</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>861</v>
+        <v>1015</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>862</v>
+        <v>1016</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>863</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="72">
+      <c r="C3" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D3" s="73">
+      <c r="D3" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E3" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F3" s="74">
+      <c r="E3" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F3" s="102">
         <v>47500.0</v>
       </c>
       <c r="G3" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="74" t="s">
-        <v>864</v>
+      <c r="H3" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>865</v>
-      </c>
-      <c r="J3" s="74">
+        <v>1019</v>
+      </c>
+      <c r="J3" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -8862,28 +10135,28 @@
       <c r="B4" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="72">
+      <c r="C4" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E4" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F4" s="74">
+      <c r="E4" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F4" s="102">
         <v>32500.0</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="74" t="s">
-        <v>864</v>
+      <c r="H4" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I4" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="74">
+      <c r="J4" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -8894,28 +10167,28 @@
       <c r="B5" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="72">
+      <c r="C5" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E5" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F5" s="74">
+      <c r="E5" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F5" s="102">
         <v>20000.0</v>
       </c>
       <c r="G5" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="74" t="s">
-        <v>864</v>
+      <c r="H5" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I5" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="74">
+      <c r="J5" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -8926,28 +10199,28 @@
       <c r="B6" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="72">
+      <c r="C6" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E6" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F6" s="74">
+      <c r="E6" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="102">
         <v>27500.0</v>
       </c>
       <c r="G6" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="74" t="s">
-        <v>864</v>
+      <c r="H6" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I6" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="74">
+      <c r="J6" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -8955,31 +10228,31 @@
       <c r="A7" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="72">
+      <c r="C7" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E7" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="74">
+      <c r="E7" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="102">
         <v>32500.0</v>
       </c>
-      <c r="G7" s="75" t="s">
+      <c r="G7" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I7" s="75" t="s">
+      <c r="H7" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I7" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -8990,28 +10263,28 @@
       <c r="B8" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="72">
+      <c r="C8" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E8" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F8" s="74">
+      <c r="E8" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F8" s="102">
         <v>20000.0</v>
       </c>
       <c r="G8" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="74" t="s">
-        <v>864</v>
+      <c r="H8" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I8" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9022,28 +10295,28 @@
       <c r="B9" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="72">
+      <c r="C9" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E9" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F9" s="74">
+      <c r="E9" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F9" s="102">
         <v>20000.0</v>
       </c>
       <c r="G9" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="74" t="s">
-        <v>864</v>
+      <c r="H9" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I9" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="J9" s="74">
+      <c r="J9" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9054,28 +10327,28 @@
       <c r="B10" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E10" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F10" s="74">
+      <c r="E10" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="102">
         <v>20000.0</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="74" t="s">
-        <v>864</v>
+      <c r="H10" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I10" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="74">
+      <c r="J10" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9086,28 +10359,28 @@
       <c r="B11" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="72">
+      <c r="C11" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E11" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F11" s="74">
+      <c r="E11" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F11" s="102">
         <v>23500.0</v>
       </c>
       <c r="G11" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="74" t="s">
-        <v>864</v>
+      <c r="H11" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I11" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="J11" s="74">
+      <c r="J11" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9118,92 +10391,92 @@
       <c r="B12" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E12" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="74">
+      <c r="E12" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="102">
         <v>40000.0</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="H12" s="74" t="s">
-        <v>864</v>
+      <c r="H12" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I12" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="J12" s="74">
+      <c r="J12" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="104" t="s">
         <v>285</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="105" t="s">
         <v>287</v>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D13" s="73">
+      <c r="D13" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E13" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="74">
+      <c r="E13" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="102">
         <v>50000.0</v>
       </c>
-      <c r="G13" s="78" t="s">
+      <c r="G13" s="106" t="s">
         <v>294</v>
       </c>
-      <c r="H13" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I13" s="78" t="s">
+      <c r="H13" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I13" s="106" t="s">
         <v>295</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="79" t="s">
+      <c r="A14" s="107" t="s">
         <v>296</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="108" t="s">
         <v>297</v>
       </c>
-      <c r="C14" s="72">
+      <c r="C14" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E14" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F14" s="74">
+      <c r="E14" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="102">
         <v>40000.0</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="109" t="s">
         <v>303</v>
       </c>
-      <c r="H14" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I14" s="81" t="s">
+      <c r="H14" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I14" s="109" t="s">
         <v>303</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9211,31 +10484,31 @@
       <c r="A15" s="38" t="s">
         <v>304</v>
       </c>
-      <c r="B15" s="82" t="s">
+      <c r="B15" s="110" t="s">
         <v>305</v>
       </c>
-      <c r="C15" s="72">
+      <c r="C15" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D15" s="73">
+      <c r="D15" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E15" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="74">
+      <c r="E15" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="102">
         <v>42500.0</v>
       </c>
       <c r="G15" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="H15" s="74" t="s">
-        <v>864</v>
+      <c r="H15" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I15" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="J15" s="74">
+      <c r="J15" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9243,63 +10516,63 @@
       <c r="A16" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="82" t="s">
+      <c r="B16" s="110" t="s">
         <v>314</v>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D16" s="73">
+      <c r="D16" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E16" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F16" s="74">
+      <c r="E16" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="102">
         <v>42500.0</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="H16" s="74" t="s">
-        <v>864</v>
+      <c r="H16" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I16" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="J16" s="74">
+      <c r="J16" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="109" t="s">
         <v>322</v>
       </c>
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="108" t="s">
         <v>323</v>
       </c>
-      <c r="C17" s="72">
+      <c r="C17" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E17" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F17" s="74">
+      <c r="E17" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F17" s="102">
         <v>60000.0</v>
       </c>
       <c r="G17" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="H17" s="74" t="s">
-        <v>864</v>
+      <c r="H17" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I17" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="J17" s="74">
+      <c r="J17" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9307,63 +10580,63 @@
       <c r="A18" s="36" t="s">
         <v>329</v>
       </c>
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="110" t="s">
         <v>330</v>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D18" s="73">
+      <c r="D18" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E18" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F18" s="74">
+      <c r="E18" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F18" s="102">
         <v>50000.0</v>
       </c>
       <c r="G18" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="H18" s="74" t="s">
-        <v>864</v>
+      <c r="H18" s="102" t="s">
+        <v>1018</v>
       </c>
       <c r="I18" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="J18" s="74">
+      <c r="J18" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="109" t="s">
         <v>339</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="108" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="72">
+      <c r="C19" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D19" s="73">
+      <c r="D19" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E19" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F19" s="74">
+      <c r="E19" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F19" s="102">
         <v>55000.0</v>
       </c>
-      <c r="G19" s="81" t="s">
+      <c r="G19" s="109" t="s">
         <v>347</v>
       </c>
-      <c r="H19" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I19" s="81" t="s">
+      <c r="H19" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I19" s="109" t="s">
         <v>348</v>
       </c>
-      <c r="J19" s="74">
+      <c r="J19" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9371,125 +10644,125 @@
       <c r="A20" s="36" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="C20" s="72">
+      <c r="C20" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D20" s="73">
+      <c r="D20" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E20" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F20" s="74">
+      <c r="E20" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F20" s="102">
         <v>50000.0</v>
       </c>
-      <c r="G20" s="81" t="s">
+      <c r="G20" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="H20" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I20" s="81" t="s">
+      <c r="H20" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I20" s="109" t="s">
         <v>357</v>
       </c>
-      <c r="J20" s="74">
+      <c r="J20" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="109" t="s">
         <v>358</v>
       </c>
-      <c r="B21" s="80" t="s">
+      <c r="B21" s="108" t="s">
         <v>359</v>
       </c>
-      <c r="C21" s="72">
+      <c r="C21" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D21" s="73">
+      <c r="D21" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E21" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="74">
+      <c r="E21" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F21" s="102">
         <v>50000.0</v>
       </c>
-      <c r="G21" s="81" t="s">
+      <c r="G21" s="109" t="s">
         <v>366</v>
       </c>
-      <c r="H21" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I21" s="81" t="s">
+      <c r="H21" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I21" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="J21" s="74">
+      <c r="J21" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="81" t="s">
+      <c r="A22" s="109" t="s">
         <v>368</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="108" t="s">
         <v>369</v>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D22" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E22" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F22" s="74">
+      <c r="E22" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F22" s="102">
         <v>45000.0</v>
       </c>
-      <c r="G22" s="81" t="s">
+      <c r="G22" s="109" t="s">
         <v>376</v>
       </c>
-      <c r="H22" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I22" s="81" t="s">
+      <c r="H22" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I22" s="109" t="s">
         <v>367</v>
       </c>
-      <c r="J22" s="74">
+      <c r="J22" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="83">
+      <c r="A23" s="111">
         <v>40664.0</v>
       </c>
       <c r="B23" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="C23" s="72">
+      <c r="C23" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D23" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E23" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F23" s="74">
+      <c r="E23" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F23" s="102">
         <v>40000.0</v>
       </c>
       <c r="G23" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I23" s="84"/>
-      <c r="J23" s="74">
+      <c r="H23" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I23" s="112"/>
+      <c r="J23" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9500,26 +10773,26 @@
       <c r="B24" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="C24" s="72">
+      <c r="C24" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D24" s="73">
+      <c r="D24" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E24" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F24" s="74">
+      <c r="E24" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F24" s="102">
         <v>35000.0</v>
       </c>
       <c r="G24" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="H24" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I24" s="84"/>
-      <c r="J24" s="74">
+      <c r="H24" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I24" s="112"/>
+      <c r="J24" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9530,26 +10803,26 @@
       <c r="B25" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="72">
+      <c r="C25" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D25" s="73">
+      <c r="D25" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E25" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F25" s="74">
+      <c r="E25" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F25" s="102">
         <v>27500.0</v>
       </c>
       <c r="G25" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="H25" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I25" s="84"/>
-      <c r="J25" s="74">
+      <c r="H25" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I25" s="112"/>
+      <c r="J25" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9560,26 +10833,26 @@
       <c r="B26" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="C26" s="72">
+      <c r="C26" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D26" s="73">
+      <c r="D26" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E26" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F26" s="74">
+      <c r="E26" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F26" s="102">
         <v>30000.0</v>
       </c>
       <c r="G26" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="H26" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I26" s="84"/>
-      <c r="J26" s="74">
+      <c r="H26" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I26" s="112"/>
+      <c r="J26" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9590,26 +10863,26 @@
       <c r="B27" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="72">
+      <c r="C27" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D27" s="73">
+      <c r="D27" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E27" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F27" s="74">
+      <c r="E27" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F27" s="102">
         <v>45000.0</v>
       </c>
       <c r="G27" s="38" t="s">
         <v>152</v>
       </c>
-      <c r="H27" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I27" s="84"/>
-      <c r="J27" s="74">
+      <c r="H27" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I27" s="112"/>
+      <c r="J27" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9620,26 +10893,26 @@
       <c r="B28" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="72">
+      <c r="C28" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D28" s="73">
+      <c r="D28" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E28" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F28" s="74">
+      <c r="E28" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F28" s="102">
         <v>35000.0</v>
       </c>
       <c r="G28" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="H28" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I28" s="84"/>
-      <c r="J28" s="74">
+      <c r="H28" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I28" s="112"/>
+      <c r="J28" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9650,26 +10923,26 @@
       <c r="B29" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D29" s="73">
+      <c r="D29" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E29" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F29" s="74">
+      <c r="E29" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F29" s="102">
         <v>40000.0</v>
       </c>
       <c r="G29" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H29" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I29" s="84"/>
-      <c r="J29" s="74">
+      <c r="H29" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I29" s="112"/>
+      <c r="J29" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9680,26 +10953,26 @@
       <c r="B30" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="72">
+      <c r="C30" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D30" s="73">
+      <c r="D30" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E30" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F30" s="74">
+      <c r="E30" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F30" s="102">
         <v>32000.0</v>
       </c>
       <c r="G30" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H30" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I30" s="84"/>
-      <c r="J30" s="74">
+      <c r="H30" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I30" s="112"/>
+      <c r="J30" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9710,26 +10983,26 @@
       <c r="B31" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C31" s="72">
+      <c r="C31" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D31" s="73">
+      <c r="D31" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E31" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F31" s="74">
+      <c r="E31" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F31" s="102">
         <v>40000.0</v>
       </c>
       <c r="G31" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I31" s="84"/>
-      <c r="J31" s="74">
+      <c r="H31" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I31" s="112"/>
+      <c r="J31" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9740,26 +11013,26 @@
       <c r="B32" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="72">
+      <c r="C32" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D32" s="73">
+      <c r="D32" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E32" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F32" s="74">
+      <c r="E32" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F32" s="102">
         <v>35000.0</v>
       </c>
       <c r="G32" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I32" s="84"/>
-      <c r="J32" s="74">
+      <c r="H32" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I32" s="112"/>
+      <c r="J32" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9770,26 +11043,26 @@
       <c r="B33" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="C33" s="72">
+      <c r="C33" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D33" s="73">
+      <c r="D33" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E33" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F33" s="74">
+      <c r="E33" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F33" s="102">
         <v>32500.0</v>
       </c>
       <c r="G33" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="H33" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I33" s="84"/>
-      <c r="J33" s="74">
+      <c r="H33" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I33" s="112"/>
+      <c r="J33" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9797,29 +11070,29 @@
       <c r="A34" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="113" t="s">
         <v>204</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D34" s="73">
+      <c r="D34" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E34" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F34" s="74">
+      <c r="E34" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F34" s="102">
         <v>37500.0</v>
       </c>
       <c r="G34" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="H34" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I34" s="84"/>
-      <c r="J34" s="74">
+      <c r="H34" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I34" s="112"/>
+      <c r="J34" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9830,26 +11103,26 @@
       <c r="B35" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="C35" s="72">
+      <c r="C35" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D35" s="73">
+      <c r="D35" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E35" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F35" s="74">
+      <c r="E35" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F35" s="102">
         <v>37500.0</v>
       </c>
       <c r="G35" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="H35" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I35" s="84"/>
-      <c r="J35" s="74">
+      <c r="H35" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I35" s="112"/>
+      <c r="J35" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9860,26 +11133,26 @@
       <c r="B36" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D36" s="73">
+      <c r="D36" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E36" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F36" s="74">
+      <c r="E36" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F36" s="102">
         <v>45000.0</v>
       </c>
       <c r="G36" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="H36" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I36" s="84"/>
-      <c r="J36" s="74">
+      <c r="H36" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I36" s="112"/>
+      <c r="J36" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9890,26 +11163,26 @@
       <c r="B37" s="36" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="72">
+      <c r="C37" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D37" s="73">
+      <c r="D37" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E37" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F37" s="74">
+      <c r="E37" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F37" s="102">
         <v>38000.0</v>
       </c>
       <c r="G37" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="H37" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I37" s="84"/>
-      <c r="J37" s="74">
+      <c r="H37" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I37" s="112"/>
+      <c r="J37" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9917,29 +11190,29 @@
       <c r="A38" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="B38" s="86" t="s">
+      <c r="B38" s="114" t="s">
         <v>242</v>
       </c>
-      <c r="C38" s="72">
+      <c r="C38" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D38" s="73">
+      <c r="D38" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E38" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F38" s="74">
+      <c r="E38" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F38" s="102">
         <v>45000.0</v>
       </c>
-      <c r="G38" s="75" t="s">
+      <c r="G38" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="H38" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I38" s="84"/>
-      <c r="J38" s="74">
+      <c r="H38" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I38" s="112"/>
+      <c r="J38" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9947,29 +11220,29 @@
       <c r="A39" s="38" t="s">
         <v>250</v>
       </c>
-      <c r="B39" s="86" t="s">
+      <c r="B39" s="114" t="s">
         <v>251</v>
       </c>
-      <c r="C39" s="72">
+      <c r="C39" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D39" s="73">
+      <c r="D39" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E39" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F39" s="74">
+      <c r="E39" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F39" s="102">
         <v>45000.0</v>
       </c>
-      <c r="G39" s="75" t="s">
+      <c r="G39" s="103" t="s">
         <v>232</v>
       </c>
-      <c r="H39" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I39" s="84"/>
-      <c r="J39" s="74">
+      <c r="H39" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I39" s="112"/>
+      <c r="J39" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -9977,29 +11250,29 @@
       <c r="A40" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="B40" s="86" t="s">
+      <c r="B40" s="114" t="s">
         <v>260</v>
       </c>
-      <c r="C40" s="72">
+      <c r="C40" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D40" s="73">
+      <c r="D40" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E40" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F40" s="74">
+      <c r="E40" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F40" s="102">
         <v>45000.0</v>
       </c>
-      <c r="G40" s="75" t="s">
+      <c r="G40" s="103" t="s">
         <v>232</v>
       </c>
-      <c r="H40" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I40" s="84"/>
-      <c r="J40" s="74">
+      <c r="H40" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I40" s="112"/>
+      <c r="J40" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -10007,29 +11280,29 @@
       <c r="A41" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="B41" s="86" t="s">
+      <c r="B41" s="114" t="s">
         <v>268</v>
       </c>
-      <c r="C41" s="72">
+      <c r="C41" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D41" s="73">
+      <c r="D41" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E41" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F41" s="74">
+      <c r="E41" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F41" s="102">
         <v>35000.0</v>
       </c>
-      <c r="G41" s="75" t="s">
+      <c r="G41" s="103" t="s">
         <v>275</v>
       </c>
-      <c r="H41" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I41" s="84"/>
-      <c r="J41" s="74">
+      <c r="H41" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I41" s="112"/>
+      <c r="J41" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -10037,61 +11310,61 @@
       <c r="A42" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="B42" s="86" t="s">
+      <c r="B42" s="114" t="s">
         <v>277</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D42" s="73">
+      <c r="D42" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E42" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F42" s="74">
+      <c r="E42" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F42" s="102">
         <v>40000.0</v>
       </c>
-      <c r="G42" s="75" t="s">
+      <c r="G42" s="103" t="s">
         <v>284</v>
       </c>
-      <c r="H42" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I42" s="84"/>
-      <c r="J42" s="74">
+      <c r="H42" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I42" s="112"/>
+      <c r="J42" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="87" t="s">
+      <c r="A43" s="115" t="s">
         <v>377</v>
       </c>
-      <c r="B43" s="88" t="s">
+      <c r="B43" s="116" t="s">
         <v>379</v>
       </c>
-      <c r="C43" s="72">
+      <c r="C43" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D43" s="73">
+      <c r="D43" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E43" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F43" s="74">
+      <c r="E43" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F43" s="102">
         <v>35000.0</v>
       </c>
-      <c r="G43" s="87" t="s">
+      <c r="G43" s="115" t="s">
         <v>386</v>
       </c>
-      <c r="H43" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I43" s="87" t="s">
+      <c r="H43" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I43" s="115" t="s">
         <v>387</v>
       </c>
-      <c r="J43" s="74">
+      <c r="J43" s="102">
         <v>5.0</v>
       </c>
     </row>
@@ -10099,276 +11372,276 @@
       <c r="A44" s="38" t="s">
         <v>388</v>
       </c>
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="110" t="s">
         <v>389</v>
       </c>
-      <c r="C44" s="72">
+      <c r="C44" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D44" s="73">
+      <c r="D44" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E44" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F44" s="74">
+      <c r="E44" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F44" s="102">
         <v>39500.0</v>
       </c>
       <c r="G44" s="38" t="s">
         <v>396</v>
       </c>
-      <c r="H44" s="74" t="s">
-        <v>866</v>
+      <c r="H44" s="102" t="s">
+        <v>1020</v>
       </c>
       <c r="I44" s="38" t="s">
         <v>397</v>
       </c>
-      <c r="J44" s="74">
+      <c r="J44" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="81" t="s">
+      <c r="A45" s="109" t="s">
         <v>398</v>
       </c>
-      <c r="B45" s="80" t="s">
+      <c r="B45" s="108" t="s">
         <v>399</v>
       </c>
-      <c r="C45" s="72">
+      <c r="C45" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D45" s="73">
+      <c r="D45" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E45" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F45" s="74">
+      <c r="E45" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F45" s="102">
         <v>30000.0</v>
       </c>
-      <c r="G45" s="81" t="s">
+      <c r="G45" s="109" t="s">
         <v>405</v>
       </c>
-      <c r="H45" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I45" s="84"/>
-      <c r="J45" s="74">
+      <c r="H45" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I45" s="112"/>
+      <c r="J45" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="81" t="s">
+      <c r="A46" s="109" t="s">
         <v>406</v>
       </c>
-      <c r="B46" s="80" t="s">
+      <c r="B46" s="108" t="s">
         <v>407</v>
       </c>
-      <c r="C46" s="72">
+      <c r="C46" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D46" s="73">
+      <c r="D46" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E46" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F46" s="74">
+      <c r="E46" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F46" s="102">
         <v>35000.0</v>
       </c>
       <c r="G46" s="38" t="s">
         <v>413</v>
       </c>
-      <c r="H46" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I46" s="84"/>
-      <c r="J46" s="74">
+      <c r="H46" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I46" s="112"/>
+      <c r="J46" s="102">
         <v>2.0</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="81" t="s">
+      <c r="A47" s="109" t="s">
         <v>414</v>
       </c>
-      <c r="B47" s="80" t="s">
+      <c r="B47" s="108" t="s">
         <v>415</v>
       </c>
-      <c r="C47" s="72">
+      <c r="C47" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D47" s="73">
+      <c r="D47" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E47" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F47" s="74">
+      <c r="E47" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F47" s="102">
         <v>45000.0</v>
       </c>
-      <c r="G47" s="81" t="s">
+      <c r="G47" s="109" t="s">
         <v>423</v>
       </c>
-      <c r="H47" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I47" s="81" t="s">
+      <c r="H47" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I47" s="109" t="s">
         <v>423</v>
       </c>
-      <c r="J47" s="74">
+      <c r="J47" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="81" t="s">
+      <c r="A48" s="109" t="s">
         <v>424</v>
       </c>
-      <c r="B48" s="80" t="s">
+      <c r="B48" s="108" t="s">
         <v>425</v>
       </c>
-      <c r="C48" s="72">
+      <c r="C48" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D48" s="73">
+      <c r="D48" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E48" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F48" s="74">
+      <c r="E48" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F48" s="102">
         <v>57500.0</v>
       </c>
-      <c r="G48" s="81" t="s">
+      <c r="G48" s="109" t="s">
         <v>222</v>
       </c>
-      <c r="H48" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I48" s="81" t="s">
+      <c r="H48" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I48" s="109" t="s">
         <v>433</v>
       </c>
-      <c r="J48" s="74">
+      <c r="J48" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="81" t="s">
+      <c r="A49" s="109" t="s">
         <v>434</v>
       </c>
-      <c r="B49" s="80" t="s">
+      <c r="B49" s="108" t="s">
         <v>435</v>
       </c>
-      <c r="C49" s="72">
+      <c r="C49" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D49" s="73">
+      <c r="D49" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E49" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F49" s="74">
+      <c r="E49" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F49" s="102">
         <v>30000.0</v>
       </c>
-      <c r="G49" s="81" t="s">
+      <c r="G49" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="H49" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I49" s="84"/>
-      <c r="J49" s="74">
+      <c r="H49" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I49" s="112"/>
+      <c r="J49" s="102">
         <v>1.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="81" t="s">
+      <c r="A50" s="109" t="s">
         <v>441</v>
       </c>
-      <c r="B50" s="80" t="s">
+      <c r="B50" s="108" t="s">
         <v>442</v>
       </c>
-      <c r="C50" s="72">
+      <c r="C50" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D50" s="73">
+      <c r="D50" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E50" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F50" s="74">
+      <c r="E50" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F50" s="102">
         <v>30000.0</v>
       </c>
-      <c r="G50" s="81" t="s">
+      <c r="G50" s="109" t="s">
         <v>440</v>
       </c>
-      <c r="H50" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I50" s="84"/>
-      <c r="J50" s="74">
+      <c r="H50" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I50" s="112"/>
+      <c r="J50" s="102">
         <v>1.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="81" t="s">
+      <c r="A51" s="109" t="s">
         <v>447</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="108" t="s">
         <v>448</v>
       </c>
-      <c r="C51" s="72">
+      <c r="C51" s="100">
         <v>0.3125</v>
       </c>
-      <c r="D51" s="73">
+      <c r="D51" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E51" s="74">
-        <v>5.0</v>
-      </c>
-      <c r="F51" s="74">
+      <c r="E51" s="102">
+        <v>5.0</v>
+      </c>
+      <c r="F51" s="102">
         <v>50000.0</v>
       </c>
-      <c r="G51" s="81" t="s">
+      <c r="G51" s="109" t="s">
         <v>456</v>
       </c>
-      <c r="H51" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I51" s="81" t="s">
+      <c r="H51" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I51" s="109" t="s">
         <v>457</v>
       </c>
-      <c r="J51" s="74">
+      <c r="J51" s="102">
         <v>5.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="74" t="s">
+      <c r="A52" s="102" t="s">
         <v>458</v>
       </c>
-      <c r="B52" s="74" t="s">
+      <c r="B52" s="102" t="s">
         <v>460</v>
       </c>
-      <c r="C52" s="89">
+      <c r="C52" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D52" s="73">
+      <c r="D52" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E52" s="74">
+      <c r="E52" s="102">
         <v>5.0</v>
       </c>
       <c r="F52" s="60">
         <v>47500.0</v>
       </c>
-      <c r="G52" s="74" t="s">
+      <c r="G52" s="102" t="s">
         <v>459</v>
       </c>
-      <c r="H52" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I52" s="74" t="s">
+      <c r="H52" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I52" s="102" t="s">
         <v>459</v>
       </c>
       <c r="J52" s="60">
@@ -10376,31 +11649,31 @@
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="74" t="s">
+      <c r="A53" s="102" t="s">
         <v>467</v>
       </c>
-      <c r="B53" s="74" t="s">
+      <c r="B53" s="102" t="s">
         <v>469</v>
       </c>
-      <c r="C53" s="89">
+      <c r="C53" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D53" s="73">
+      <c r="D53" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E53" s="74">
+      <c r="E53" s="102">
         <v>5.0</v>
       </c>
       <c r="F53" s="60">
         <v>40000.0</v>
       </c>
-      <c r="G53" s="74" t="s">
+      <c r="G53" s="102" t="s">
         <v>468</v>
       </c>
-      <c r="H53" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I53" s="74" t="s">
+      <c r="H53" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I53" s="102" t="s">
         <v>468</v>
       </c>
       <c r="J53" s="60">
@@ -10408,31 +11681,31 @@
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="74" t="s">
+      <c r="A54" s="102" t="s">
         <v>476</v>
       </c>
-      <c r="B54" s="74" t="s">
+      <c r="B54" s="102" t="s">
         <v>478</v>
       </c>
-      <c r="C54" s="89">
+      <c r="C54" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D54" s="73">
+      <c r="D54" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E54" s="74">
+      <c r="E54" s="102">
         <v>5.0</v>
       </c>
       <c r="F54" s="60">
         <v>40000.0</v>
       </c>
-      <c r="G54" s="74" t="s">
+      <c r="G54" s="102" t="s">
         <v>477</v>
       </c>
-      <c r="H54" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I54" s="74" t="s">
+      <c r="H54" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I54" s="102" t="s">
         <v>477</v>
       </c>
       <c r="J54" s="60">
@@ -10440,31 +11713,31 @@
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="74" t="s">
+      <c r="A55" s="102" t="s">
         <v>485</v>
       </c>
-      <c r="B55" s="74" t="s">
+      <c r="B55" s="102" t="s">
         <v>487</v>
       </c>
-      <c r="C55" s="89">
+      <c r="C55" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D55" s="73">
+      <c r="D55" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E55" s="74">
+      <c r="E55" s="102">
         <v>5.0</v>
       </c>
       <c r="F55" s="60">
         <v>67500.0</v>
       </c>
-      <c r="G55" s="74" t="s">
+      <c r="G55" s="102" t="s">
         <v>486</v>
       </c>
-      <c r="H55" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I55" s="74" t="s">
+      <c r="H55" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I55" s="102" t="s">
         <v>486</v>
       </c>
       <c r="J55" s="60">
@@ -10472,31 +11745,31 @@
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="83">
+      <c r="A56" s="111">
         <v>13575.0</v>
       </c>
-      <c r="B56" s="74" t="s">
+      <c r="B56" s="102" t="s">
         <v>494</v>
       </c>
-      <c r="C56" s="89">
+      <c r="C56" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D56" s="73">
+      <c r="D56" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E56" s="74">
+      <c r="E56" s="102">
         <v>5.0</v>
       </c>
       <c r="F56" s="60">
         <v>42500.0</v>
       </c>
-      <c r="G56" s="74" t="s">
+      <c r="G56" s="102" t="s">
         <v>493</v>
       </c>
-      <c r="H56" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I56" s="74" t="s">
+      <c r="H56" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I56" s="102" t="s">
         <v>493</v>
       </c>
       <c r="J56" s="60">
@@ -10504,31 +11777,31 @@
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="74" t="s">
+      <c r="A57" s="102" t="s">
         <v>500</v>
       </c>
-      <c r="B57" s="74" t="s">
+      <c r="B57" s="102" t="s">
         <v>502</v>
       </c>
-      <c r="C57" s="89">
+      <c r="C57" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D57" s="73">
+      <c r="D57" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E57" s="74">
+      <c r="E57" s="102">
         <v>5.0</v>
       </c>
       <c r="F57" s="60">
         <v>50000.0</v>
       </c>
-      <c r="G57" s="74" t="s">
+      <c r="G57" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="H57" s="74" t="s">
-        <v>864</v>
-      </c>
-      <c r="I57" s="74" t="s">
+      <c r="H57" s="102" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I57" s="102" t="s">
         <v>501</v>
       </c>
       <c r="J57" s="60">
@@ -10536,31 +11809,31 @@
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="81" t="s">
+      <c r="A58" s="109" t="s">
         <v>509</v>
       </c>
-      <c r="B58" s="81" t="s">
+      <c r="B58" s="109" t="s">
         <v>511</v>
       </c>
-      <c r="C58" s="89">
+      <c r="C58" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D58" s="73">
+      <c r="D58" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E58" s="74">
+      <c r="E58" s="102">
         <v>5.0</v>
       </c>
       <c r="F58" s="60">
         <v>60000.0</v>
       </c>
-      <c r="G58" s="81" t="s">
+      <c r="G58" s="109" t="s">
         <v>510</v>
       </c>
-      <c r="H58" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I58" s="81" t="s">
+      <c r="H58" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I58" s="109" t="s">
         <v>510</v>
       </c>
       <c r="J58" s="60">
@@ -10568,31 +11841,31 @@
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="81" t="s">
+      <c r="A59" s="109" t="s">
         <v>517</v>
       </c>
-      <c r="B59" s="81" t="s">
+      <c r="B59" s="109" t="s">
         <v>519</v>
       </c>
-      <c r="C59" s="89">
+      <c r="C59" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D59" s="73">
+      <c r="D59" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E59" s="74">
+      <c r="E59" s="102">
         <v>5.0</v>
       </c>
       <c r="F59" s="60">
         <v>35000.0</v>
       </c>
-      <c r="G59" s="81" t="s">
+      <c r="G59" s="109" t="s">
         <v>518</v>
       </c>
-      <c r="H59" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I59" s="81" t="s">
+      <c r="H59" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I59" s="109" t="s">
         <v>518</v>
       </c>
       <c r="J59" s="60">
@@ -10600,31 +11873,31 @@
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="81" t="s">
+      <c r="A60" s="109" t="s">
         <v>525</v>
       </c>
-      <c r="B60" s="81" t="s">
+      <c r="B60" s="109" t="s">
         <v>527</v>
       </c>
-      <c r="C60" s="89">
+      <c r="C60" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D60" s="73">
+      <c r="D60" s="101">
         <v>0.5972222222222222</v>
       </c>
-      <c r="E60" s="74">
+      <c r="E60" s="102">
         <v>5.0</v>
       </c>
       <c r="F60" s="60">
         <v>55000.0</v>
       </c>
-      <c r="G60" s="81" t="s">
+      <c r="G60" s="109" t="s">
         <v>526</v>
       </c>
-      <c r="H60" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I60" s="81" t="s">
+      <c r="H60" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I60" s="109" t="s">
         <v>526</v>
       </c>
       <c r="J60" s="60">
@@ -10632,31 +11905,31 @@
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="109" t="s">
         <v>532</v>
       </c>
-      <c r="B61" s="81" t="s">
+      <c r="B61" s="109" t="s">
         <v>534</v>
       </c>
-      <c r="C61" s="89">
+      <c r="C61" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D61" s="73">
+      <c r="D61" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E61" s="74">
+      <c r="E61" s="102">
         <v>5.0</v>
       </c>
       <c r="F61" s="60">
         <v>40000.0</v>
       </c>
-      <c r="G61" s="81" t="s">
+      <c r="G61" s="109" t="s">
         <v>533</v>
       </c>
-      <c r="H61" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I61" s="81" t="s">
+      <c r="H61" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I61" s="109" t="s">
         <v>533</v>
       </c>
       <c r="J61" s="60">
@@ -10664,31 +11937,31 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="71" t="s">
+      <c r="A62" s="99" t="s">
         <v>540</v>
       </c>
-      <c r="B62" s="81" t="s">
+      <c r="B62" s="109" t="s">
         <v>542</v>
       </c>
-      <c r="C62" s="89">
+      <c r="C62" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D62" s="73">
+      <c r="D62" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E62" s="74">
+      <c r="E62" s="102">
         <v>5.0</v>
       </c>
       <c r="F62" s="60">
         <v>40000.0</v>
       </c>
-      <c r="G62" s="81" t="s">
+      <c r="G62" s="109" t="s">
         <v>541</v>
       </c>
-      <c r="H62" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I62" s="81" t="s">
+      <c r="H62" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I62" s="109" t="s">
         <v>541</v>
       </c>
       <c r="J62" s="60">
@@ -10696,31 +11969,31 @@
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="81" t="s">
+      <c r="A63" s="109" t="s">
         <v>549</v>
       </c>
-      <c r="B63" s="81" t="s">
+      <c r="B63" s="109" t="s">
         <v>551</v>
       </c>
-      <c r="C63" s="89">
+      <c r="C63" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D63" s="73">
+      <c r="D63" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E63" s="74">
+      <c r="E63" s="102">
         <v>5.0</v>
       </c>
       <c r="F63" s="60">
         <v>50000.0</v>
       </c>
-      <c r="G63" s="81" t="s">
+      <c r="G63" s="109" t="s">
         <v>550</v>
       </c>
-      <c r="H63" s="74" t="s">
-        <v>866</v>
-      </c>
-      <c r="I63" s="81" t="s">
+      <c r="H63" s="102" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I63" s="109" t="s">
         <v>550</v>
       </c>
       <c r="J63" s="60">
@@ -10728,27 +12001,27 @@
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="83">
+      <c r="A64" s="111">
         <v>36526.0</v>
       </c>
       <c r="B64" s="38" t="s">
         <v>512</v>
       </c>
-      <c r="C64" s="89">
+      <c r="C64" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D64" s="73">
+      <c r="D64" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E64" s="74">
+      <c r="E64" s="102">
         <v>5.0</v>
       </c>
       <c r="F64" s="48"/>
       <c r="G64" s="38" t="s">
         <v>558</v>
       </c>
-      <c r="H64" s="74" t="s">
-        <v>867</v>
+      <c r="H64" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I64" s="38" t="s">
         <v>558</v>
@@ -10764,21 +12037,21 @@
       <c r="B65" s="38" t="s">
         <v>564</v>
       </c>
-      <c r="C65" s="89">
+      <c r="C65" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D65" s="73">
+      <c r="D65" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E65" s="74">
+      <c r="E65" s="102">
         <v>5.0</v>
       </c>
       <c r="F65" s="48"/>
       <c r="G65" s="38" t="s">
         <v>563</v>
       </c>
-      <c r="H65" s="74" t="s">
-        <v>867</v>
+      <c r="H65" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I65" s="38" t="s">
         <v>563</v>
@@ -10788,27 +12061,27 @@
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="71">
+      <c r="A66" s="99">
         <v>38718.0</v>
       </c>
       <c r="B66" s="38" t="s">
         <v>568</v>
       </c>
-      <c r="C66" s="89">
+      <c r="C66" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D66" s="73">
+      <c r="D66" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E66" s="74">
+      <c r="E66" s="102">
         <v>5.0</v>
       </c>
       <c r="F66" s="48"/>
       <c r="G66" s="38" t="s">
         <v>567</v>
       </c>
-      <c r="H66" s="74" t="s">
-        <v>867</v>
+      <c r="H66" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I66" s="38" t="s">
         <v>567</v>
@@ -10824,21 +12097,21 @@
       <c r="B67" s="38" t="s">
         <v>574</v>
       </c>
-      <c r="C67" s="89">
+      <c r="C67" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D67" s="73">
+      <c r="D67" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E67" s="74">
+      <c r="E67" s="102">
         <v>5.0</v>
       </c>
       <c r="F67" s="48"/>
       <c r="G67" s="38" t="s">
         <v>510</v>
       </c>
-      <c r="H67" s="74" t="s">
-        <v>867</v>
+      <c r="H67" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I67" s="38" t="s">
         <v>510</v>
@@ -10848,19 +12121,19 @@
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="71">
+      <c r="A68" s="99">
         <v>39814.0</v>
       </c>
       <c r="B68" s="38" t="s">
         <v>580</v>
       </c>
-      <c r="C68" s="89">
+      <c r="C68" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D68" s="73">
+      <c r="D68" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E68" s="74">
+      <c r="E68" s="102">
         <v>5.0</v>
       </c>
       <c r="F68" s="60">
@@ -10869,8 +12142,8 @@
       <c r="G68" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="H68" s="74" t="s">
-        <v>867</v>
+      <c r="H68" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I68" s="38" t="s">
         <v>579</v>
@@ -10886,13 +12159,13 @@
       <c r="B69" s="36" t="s">
         <v>588</v>
       </c>
-      <c r="C69" s="89">
+      <c r="C69" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D69" s="73">
+      <c r="D69" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E69" s="74">
+      <c r="E69" s="102">
         <v>5.0</v>
       </c>
       <c r="F69" s="60">
@@ -10901,8 +12174,8 @@
       <c r="G69" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="H69" s="74" t="s">
-        <v>867</v>
+      <c r="H69" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I69" s="38" t="s">
         <v>587</v>
@@ -10918,13 +12191,13 @@
       <c r="B70" s="38" t="s">
         <v>596</v>
       </c>
-      <c r="C70" s="89">
+      <c r="C70" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D70" s="73">
+      <c r="D70" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E70" s="74">
+      <c r="E70" s="102">
         <v>5.0</v>
       </c>
       <c r="F70" s="60">
@@ -10933,8 +12206,8 @@
       <c r="G70" s="38" t="s">
         <v>595</v>
       </c>
-      <c r="H70" s="74" t="s">
-        <v>867</v>
+      <c r="H70" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I70" s="38" t="s">
         <v>595</v>
@@ -10950,13 +12223,13 @@
       <c r="B71" s="38" t="s">
         <v>604</v>
       </c>
-      <c r="C71" s="89">
+      <c r="C71" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D71" s="73">
+      <c r="D71" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E71" s="74">
+      <c r="E71" s="102">
         <v>5.0</v>
       </c>
       <c r="F71" s="60">
@@ -10965,8 +12238,8 @@
       <c r="G71" s="38" t="s">
         <v>603</v>
       </c>
-      <c r="H71" s="74" t="s">
-        <v>867</v>
+      <c r="H71" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I71" s="38" t="s">
         <v>603</v>
@@ -10982,13 +12255,13 @@
       <c r="B72" s="38" t="s">
         <v>611</v>
       </c>
-      <c r="C72" s="89">
+      <c r="C72" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D72" s="73">
+      <c r="D72" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E72" s="74">
+      <c r="E72" s="102">
         <v>5.0</v>
       </c>
       <c r="F72" s="60">
@@ -10997,8 +12270,8 @@
       <c r="G72" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="H72" s="74" t="s">
-        <v>867</v>
+      <c r="H72" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I72" s="38" t="s">
         <v>587</v>
@@ -11014,13 +12287,13 @@
       <c r="B73" s="38" t="s">
         <v>619</v>
       </c>
-      <c r="C73" s="89">
+      <c r="C73" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D73" s="73">
+      <c r="D73" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E73" s="74">
+      <c r="E73" s="102">
         <v>5.0</v>
       </c>
       <c r="F73" s="60">
@@ -11029,8 +12302,8 @@
       <c r="G73" s="38" t="s">
         <v>618</v>
       </c>
-      <c r="H73" s="74" t="s">
-        <v>867</v>
+      <c r="H73" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I73" s="38" t="s">
         <v>618</v>
@@ -11046,13 +12319,13 @@
       <c r="B74" s="38" t="s">
         <v>627</v>
       </c>
-      <c r="C74" s="89">
+      <c r="C74" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D74" s="73">
+      <c r="D74" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E74" s="74">
+      <c r="E74" s="102">
         <v>5.0</v>
       </c>
       <c r="F74" s="60">
@@ -11061,8 +12334,8 @@
       <c r="G74" s="38" t="s">
         <v>626</v>
       </c>
-      <c r="H74" s="74" t="s">
-        <v>867</v>
+      <c r="H74" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I74" s="38" t="s">
         <v>626</v>
@@ -11078,13 +12351,13 @@
       <c r="B75" s="38" t="s">
         <v>633</v>
       </c>
-      <c r="C75" s="89">
+      <c r="C75" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D75" s="73">
+      <c r="D75" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E75" s="74">
+      <c r="E75" s="102">
         <v>5.0</v>
       </c>
       <c r="F75" s="60">
@@ -11093,8 +12366,8 @@
       <c r="G75" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="H75" s="74" t="s">
-        <v>867</v>
+      <c r="H75" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I75" s="38" t="s">
         <v>587</v>
@@ -11110,13 +12383,13 @@
       <c r="B76" s="38" t="s">
         <v>640</v>
       </c>
-      <c r="C76" s="89">
+      <c r="C76" s="117">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D76" s="73">
+      <c r="D76" s="101">
         <v>0.7083333333333334</v>
       </c>
-      <c r="E76" s="74">
+      <c r="E76" s="102">
         <v>0.0</v>
       </c>
       <c r="F76" s="60">
@@ -11125,8 +12398,8 @@
       <c r="G76" s="38" t="s">
         <v>587</v>
       </c>
-      <c r="H76" s="74" t="s">
-        <v>867</v>
+      <c r="H76" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I76" s="38" t="s">
         <v>587</v>
@@ -11142,13 +12415,13 @@
       <c r="B77" s="38" t="s">
         <v>647</v>
       </c>
-      <c r="C77" s="89">
+      <c r="C77" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D77" s="73">
+      <c r="D77" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E77" s="74">
+      <c r="E77" s="102">
         <v>5.0</v>
       </c>
       <c r="F77" s="60">
@@ -11157,8 +12430,8 @@
       <c r="G77" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="H77" s="74" t="s">
-        <v>867</v>
+      <c r="H77" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I77" s="38" t="s">
         <v>160</v>
@@ -11174,13 +12447,13 @@
       <c r="B78" s="38" t="s">
         <v>653</v>
       </c>
-      <c r="C78" s="89">
+      <c r="C78" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D78" s="73">
+      <c r="D78" s="101">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E78" s="74">
+      <c r="E78" s="102">
         <v>5.0</v>
       </c>
       <c r="F78" s="60">
@@ -11189,8 +12462,8 @@
       <c r="G78" s="38" t="s">
         <v>603</v>
       </c>
-      <c r="H78" s="74" t="s">
-        <v>867</v>
+      <c r="H78" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I78" s="38" t="s">
         <v>603</v>
@@ -11206,13 +12479,13 @@
       <c r="B79" s="38" t="s">
         <v>662</v>
       </c>
-      <c r="C79" s="89">
+      <c r="C79" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D79" s="73">
+      <c r="D79" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E79" s="74">
+      <c r="E79" s="102">
         <v>5.0</v>
       </c>
       <c r="F79" s="60">
@@ -11221,8 +12494,8 @@
       <c r="G79" s="38" t="s">
         <v>661</v>
       </c>
-      <c r="H79" s="74" t="s">
-        <v>867</v>
+      <c r="H79" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I79" s="38" t="s">
         <v>661</v>
@@ -11238,13 +12511,13 @@
       <c r="B80" s="38" t="s">
         <v>669</v>
       </c>
-      <c r="C80" s="89">
+      <c r="C80" s="117">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D80" s="73">
+      <c r="D80" s="101">
         <v>0.6875</v>
       </c>
-      <c r="E80" s="74">
+      <c r="E80" s="102">
         <v>5.0</v>
       </c>
       <c r="F80" s="60">
@@ -11253,8 +12526,8 @@
       <c r="G80" s="38" t="s">
         <v>661</v>
       </c>
-      <c r="H80" s="74" t="s">
-        <v>867</v>
+      <c r="H80" s="102" t="s">
+        <v>1021</v>
       </c>
       <c r="I80" s="38" t="s">
         <v>160</v>
@@ -11264,19 +12537,19 @@
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="71">
+      <c r="A81" s="99">
         <v>38353.0</v>
       </c>
       <c r="B81" s="38" t="s">
         <v>677</v>
       </c>
-      <c r="C81" s="90">
+      <c r="C81" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D81" s="91">
+      <c r="D81" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E81" s="92">
+      <c r="E81" s="120">
         <v>5.0</v>
       </c>
       <c r="F81" s="38"/>
@@ -11284,7 +12557,7 @@
         <v>676</v>
       </c>
       <c r="H81" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I81" s="38" t="s">
         <v>676</v>
@@ -11300,13 +12573,13 @@
       <c r="B82" s="38" t="s">
         <v>684</v>
       </c>
-      <c r="C82" s="90">
+      <c r="C82" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D82" s="91">
+      <c r="D82" s="119">
         <v>0.6666666666666666</v>
       </c>
-      <c r="E82" s="92">
+      <c r="E82" s="120">
         <v>5.0</v>
       </c>
       <c r="F82" s="38">
@@ -11316,7 +12589,7 @@
         <v>683</v>
       </c>
       <c r="H82" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I82" s="38" t="s">
         <v>683</v>
@@ -11332,13 +12605,13 @@
       <c r="B83" s="38" t="s">
         <v>692</v>
       </c>
-      <c r="C83" s="90">
+      <c r="C83" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D83" s="91">
+      <c r="D83" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E83" s="92">
+      <c r="E83" s="120">
         <v>5.0</v>
       </c>
       <c r="F83" s="38">
@@ -11348,7 +12621,7 @@
         <v>691</v>
       </c>
       <c r="H83" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I83" s="38" t="s">
         <v>691</v>
@@ -11364,13 +12637,13 @@
       <c r="B84" s="36" t="s">
         <v>700</v>
       </c>
-      <c r="C84" s="90">
+      <c r="C84" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D84" s="91">
+      <c r="D84" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E84" s="92">
+      <c r="E84" s="120">
         <v>5.0</v>
       </c>
       <c r="F84" s="38">
@@ -11380,7 +12653,7 @@
         <v>699</v>
       </c>
       <c r="H84" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I84" s="38" t="s">
         <v>699</v>
@@ -11396,13 +12669,13 @@
       <c r="B85" s="38" t="s">
         <v>708</v>
       </c>
-      <c r="C85" s="90">
+      <c r="C85" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D85" s="91">
+      <c r="D85" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E85" s="92">
+      <c r="E85" s="120">
         <v>5.0</v>
       </c>
       <c r="F85" s="36">
@@ -11412,7 +12685,7 @@
         <v>707</v>
       </c>
       <c r="H85" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I85" s="36" t="s">
         <v>707</v>
@@ -11428,13 +12701,13 @@
       <c r="B86" s="38" t="s">
         <v>716</v>
       </c>
-      <c r="C86" s="90">
+      <c r="C86" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D86" s="91">
+      <c r="D86" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E86" s="92">
+      <c r="E86" s="120">
         <v>5.0</v>
       </c>
       <c r="F86" s="38">
@@ -11444,7 +12717,7 @@
         <v>715</v>
       </c>
       <c r="H86" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I86" s="38" t="s">
         <v>715</v>
@@ -11460,13 +12733,13 @@
       <c r="B87" s="38" t="s">
         <v>722</v>
       </c>
-      <c r="C87" s="90">
+      <c r="C87" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D87" s="91">
+      <c r="D87" s="119">
         <v>0.6875</v>
       </c>
-      <c r="E87" s="92">
+      <c r="E87" s="120">
         <v>5.0</v>
       </c>
       <c r="F87" s="38">
@@ -11476,7 +12749,7 @@
         <v>661</v>
       </c>
       <c r="H87" s="44" t="s">
-        <v>868</v>
+        <v>1022</v>
       </c>
       <c r="I87" s="38" t="s">
         <v>661</v>
@@ -11492,10 +12765,10 @@
       <c r="B88" s="38" t="s">
         <v>730</v>
       </c>
-      <c r="C88" s="90">
+      <c r="C88" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D88" s="73">
+      <c r="D88" s="101">
         <v>0.6666666666666666</v>
       </c>
       <c r="E88" s="60">
@@ -11507,8 +12780,8 @@
       <c r="G88" s="38" t="s">
         <v>729</v>
       </c>
-      <c r="H88" s="93" t="s">
-        <v>869</v>
+      <c r="H88" s="121" t="s">
+        <v>1023</v>
       </c>
       <c r="I88" s="38" t="s">
         <v>729</v>
@@ -11524,10 +12797,10 @@
       <c r="B89" s="38" t="s">
         <v>736</v>
       </c>
-      <c r="C89" s="90">
+      <c r="C89" s="118">
         <v>0.2916666666666667</v>
       </c>
-      <c r="D89" s="73">
+      <c r="D89" s="101">
         <v>0.6666666666666666</v>
       </c>
       <c r="E89" s="60">
@@ -11539,8 +12812,8 @@
       <c r="G89" s="38" t="s">
         <v>735</v>
       </c>
-      <c r="H89" s="93" t="s">
-        <v>869</v>
+      <c r="H89" s="121" t="s">
+        <v>1023</v>
       </c>
       <c r="I89" s="38" t="s">
         <v>735</v>
@@ -11556,10 +12829,10 @@
       <c r="B90" s="38" t="s">
         <v>744</v>
       </c>
-      <c r="C90" s="38" t="s">
-        <v>744</v>
-      </c>
-      <c r="D90" s="73">
+      <c r="C90" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D90" s="101">
         <v>0.6666666666666666</v>
       </c>
       <c r="E90" s="60">
@@ -11571,8 +12844,8 @@
       <c r="G90" s="38" t="s">
         <v>743</v>
       </c>
-      <c r="H90" s="93" t="s">
-        <v>870</v>
+      <c r="H90" s="121" t="s">
+        <v>1024</v>
       </c>
       <c r="I90" s="38" t="s">
         <v>743</v>
@@ -11588,10 +12861,10 @@
       <c r="B91" s="38" t="s">
         <v>752</v>
       </c>
-      <c r="C91" s="38" t="s">
-        <v>752</v>
-      </c>
-      <c r="D91" s="91">
+      <c r="C91" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D91" s="119">
         <v>0.6875</v>
       </c>
       <c r="E91" s="60">
@@ -11603,8 +12876,8 @@
       <c r="G91" s="38" t="s">
         <v>751</v>
       </c>
-      <c r="H91" s="93" t="s">
-        <v>870</v>
+      <c r="H91" s="121" t="s">
+        <v>1024</v>
       </c>
       <c r="I91" s="38" t="s">
         <v>751</v>
@@ -11620,10 +12893,10 @@
       <c r="B92" s="38" t="s">
         <v>760</v>
       </c>
-      <c r="C92" s="38" t="s">
-        <v>760</v>
-      </c>
-      <c r="D92" s="91">
+      <c r="C92" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D92" s="119">
         <v>0.6875</v>
       </c>
       <c r="E92" s="60">
@@ -11635,8 +12908,8 @@
       <c r="G92" s="38" t="s">
         <v>759</v>
       </c>
-      <c r="H92" s="93" t="s">
-        <v>870</v>
+      <c r="H92" s="121" t="s">
+        <v>1024</v>
       </c>
       <c r="I92" s="38" t="s">
         <v>759</v>
@@ -11646,45 +12919,879 @@
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="E93" s="55"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
+      <c r="A93" s="10" t="s">
+        <v>766</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C93" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D93" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E93" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G93" s="38" t="s">
+        <v>767</v>
+      </c>
+      <c r="I93" s="38" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C94" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D94" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E94" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C95" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D95" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E95" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="C96" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D96" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E96" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="10" t="s">
+        <v>796</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="C97" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D97" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E97" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="C98" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D98" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E98" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="10" t="s">
+        <v>810</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C99" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D99" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E99" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="C100" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D100" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E100" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="C101" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D101" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E101" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="60" t="s">
+        <v>830</v>
+      </c>
+      <c r="B102" s="60" t="s">
+        <v>832</v>
+      </c>
+      <c r="C102" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D102" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E102" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G102" s="60" t="s">
+        <v>831</v>
+      </c>
+      <c r="I102" s="60" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="63" t="s">
+        <v>835</v>
+      </c>
+      <c r="B103" s="63" t="s">
+        <v>837</v>
+      </c>
+      <c r="C103" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D103" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E103" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G103" s="60" t="s">
+        <v>836</v>
+      </c>
+      <c r="I103" s="60" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="65">
+        <v>36982.0</v>
+      </c>
+      <c r="B104" s="63" t="s">
+        <v>844</v>
+      </c>
+      <c r="C104" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D104" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E104" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G104" s="60" t="s">
+        <v>843</v>
+      </c>
+      <c r="I104" s="60" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="68">
+        <v>37347.0</v>
+      </c>
+      <c r="B105" s="46" t="s">
+        <v>849</v>
+      </c>
+      <c r="C105" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D105" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E105" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G105" s="60" t="s">
+        <v>848</v>
+      </c>
+      <c r="I105" s="60" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="38" t="s">
+        <v>525</v>
+      </c>
+      <c r="B106" s="38" t="s">
+        <v>527</v>
+      </c>
+      <c r="C106" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D106" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E106" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G106" s="60" t="s">
+        <v>853</v>
+      </c>
+      <c r="I106" s="60" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="60" t="s">
+        <v>857</v>
+      </c>
+      <c r="B107" s="60" t="s">
+        <v>859</v>
+      </c>
+      <c r="C107" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D107" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E107" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G107" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="I107" s="60" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="60" t="s">
+        <v>862</v>
+      </c>
+      <c r="B108" s="60" t="s">
+        <v>863</v>
+      </c>
+      <c r="C108" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D108" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E108" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G108" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="I108" s="60" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="60" t="s">
+        <v>866</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>867</v>
+      </c>
+      <c r="C109" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D109" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E109" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G109" s="60" t="s">
+        <v>858</v>
+      </c>
+      <c r="I109" s="60" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="60" t="s">
+        <v>870</v>
+      </c>
+      <c r="B110" s="60" t="s">
+        <v>872</v>
+      </c>
+      <c r="C110" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D110" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E110" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G110" s="60" t="s">
+        <v>871</v>
+      </c>
+      <c r="I110" s="60" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="60" t="s">
+        <v>876</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>877</v>
+      </c>
+      <c r="C111" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D111" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E111" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G111" s="60" t="s">
+        <v>871</v>
+      </c>
+      <c r="I111" s="60" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="74" t="s">
+        <v>500</v>
+      </c>
+      <c r="B112" s="75" t="s">
+        <v>883</v>
+      </c>
+      <c r="C112" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D112" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E112" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G112" s="60" t="s">
+        <v>882</v>
+      </c>
+      <c r="I112" s="60" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="60" t="s">
+        <v>888</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>890</v>
+      </c>
+      <c r="C113" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D113" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E113" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G113" s="60" t="s">
+        <v>889</v>
+      </c>
+      <c r="I113" s="60" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="78">
+        <v>14642.0</v>
+      </c>
+      <c r="B114" s="81" t="s">
+        <v>898</v>
+      </c>
+      <c r="C114" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D114" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E114" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G114" s="80" t="s">
+        <v>897</v>
+      </c>
+      <c r="I114" s="80" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="78">
+        <v>19391.0</v>
+      </c>
+      <c r="B115" s="81" t="s">
+        <v>905</v>
+      </c>
+      <c r="C115" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D115" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E115" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G115" s="80" t="s">
+        <v>904</v>
+      </c>
+      <c r="I115" s="80" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="78">
+        <v>20121.0</v>
+      </c>
+      <c r="B116" s="81" t="s">
+        <v>912</v>
+      </c>
+      <c r="C116" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D116" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E116" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G116" s="80" t="s">
+        <v>911</v>
+      </c>
+      <c r="I116" s="80" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="78">
+        <v>24139.0</v>
+      </c>
+      <c r="B117" s="81" t="s">
+        <v>919</v>
+      </c>
+      <c r="C117" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D117" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E117" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G117" s="80" t="s">
+        <v>918</v>
+      </c>
+      <c r="I117" s="80" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="78">
+        <v>24504.0</v>
+      </c>
+      <c r="B118" s="81" t="s">
+        <v>926</v>
+      </c>
+      <c r="C118" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D118" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E118" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G118" s="80" t="s">
+        <v>925</v>
+      </c>
+      <c r="I118" s="80" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="78">
+        <v>25600.0</v>
+      </c>
+      <c r="B119" s="81" t="s">
+        <v>933</v>
+      </c>
+      <c r="C119" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D119" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E119" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G119" s="80" t="s">
+        <v>932</v>
+      </c>
+      <c r="I119" s="80" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="78">
+        <v>25965.0</v>
+      </c>
+      <c r="B120" s="81" t="s">
+        <v>940</v>
+      </c>
+      <c r="C120" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D120" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E120" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G120" s="80" t="s">
+        <v>939</v>
+      </c>
+      <c r="I120" s="80" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="86" t="s">
+        <v>946</v>
+      </c>
+      <c r="B121" s="86" t="s">
+        <v>948</v>
+      </c>
+      <c r="C121" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D121" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E121" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G121" s="86" t="s">
+        <v>947</v>
+      </c>
+      <c r="I121" s="86" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="86" t="s">
+        <v>954</v>
+      </c>
+      <c r="B122" s="86" t="s">
+        <v>957</v>
+      </c>
+      <c r="C122" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D122" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E122" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G122" s="86" t="s">
+        <v>956</v>
+      </c>
+      <c r="I122" s="86" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="86" t="s">
+        <v>963</v>
+      </c>
+      <c r="B123" s="86" t="s">
+        <v>966</v>
+      </c>
+      <c r="C123" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D123" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E123" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G123" s="86" t="s">
+        <v>965</v>
+      </c>
+      <c r="I123" s="86" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="86" t="s">
+        <v>973</v>
+      </c>
+      <c r="B124" s="86" t="s">
+        <v>974</v>
+      </c>
+      <c r="C124" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D124" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E124" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G124" s="86" t="s">
+        <v>956</v>
+      </c>
+      <c r="I124" s="86" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="86" t="s">
+        <v>980</v>
+      </c>
+      <c r="B125" s="86" t="s">
+        <v>983</v>
+      </c>
+      <c r="C125" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D125" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E125" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G125" s="86" t="s">
+        <v>982</v>
+      </c>
+      <c r="I125" s="86" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="86" t="s">
+        <v>989</v>
+      </c>
+      <c r="B126" s="86" t="s">
+        <v>991</v>
+      </c>
+      <c r="C126" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D126" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E126" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G126" s="86" t="s">
+        <v>990</v>
+      </c>
+      <c r="I126" s="86" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="86" t="s">
+        <v>994</v>
+      </c>
+      <c r="B127" s="86" t="s">
+        <v>995</v>
+      </c>
+      <c r="C127" s="122">
+        <v>0.3125</v>
+      </c>
+      <c r="D127" s="122">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="E127" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G127" s="86" t="s">
+        <v>982</v>
+      </c>
+      <c r="I127" s="86" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="67" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B128" s="93" t="s">
+        <v>114</v>
+      </c>
+      <c r="C128" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D128" s="122">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="E128" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G128" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I128" s="92" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="94" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B129" s="94" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C129" s="122">
+        <v>0.375</v>
+      </c>
+      <c r="D129" s="122">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="E129" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G129" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I129" s="92" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="96" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B130" s="98" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C130" s="118">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="D130" s="119">
+        <v>0.6875</v>
+      </c>
+      <c r="E130" s="60">
+        <v>5.0</v>
+      </c>
+      <c r="G130" s="92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I130" s="92" t="s">
+        <v>1002</v>
+      </c>
+    </row>
     <row r="131" ht="15.75" customHeight="1"/>
     <row r="132" ht="15.75" customHeight="1"/>
     <row r="133" ht="15.75" customHeight="1"/>
@@ -12578,216 +14685,216 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.0" customHeight="1">
-      <c r="A1" s="94" t="s">
-        <v>871</v>
+      <c r="A1" s="123" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="95" t="s">
-        <v>872</v>
-      </c>
-      <c r="B3" s="96"/>
+      <c r="A3" s="124" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B3" s="125"/>
     </row>
     <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="97" t="s">
-        <v>873</v>
-      </c>
-      <c r="B4" s="97" t="s">
-        <v>874</v>
+      <c r="A4" s="126" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B4" s="126" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="97" t="s">
-        <v>875</v>
-      </c>
-      <c r="B5" s="98" t="s">
-        <v>876</v>
+      <c r="A5" s="126" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B5" s="127" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1">
-      <c r="A6" s="97" t="s">
-        <v>877</v>
-      </c>
-      <c r="B6" s="98" t="s">
-        <v>878</v>
+      <c r="A6" s="126" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>1032</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="97" t="s">
-        <v>879</v>
-      </c>
-      <c r="B7" s="97" t="s">
-        <v>880</v>
+      <c r="A7" s="126" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B7" s="126" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="8" ht="6.0" customHeight="1"/>
     <row r="9" ht="13.5" customHeight="1">
-      <c r="A9" s="95" t="s">
-        <v>881</v>
-      </c>
-      <c r="B9" s="96"/>
+      <c r="A9" s="124" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B9" s="125"/>
     </row>
     <row r="10" ht="13.5" customHeight="1">
-      <c r="A10" s="97" t="s">
-        <v>882</v>
-      </c>
-      <c r="B10" s="97" t="s">
-        <v>883</v>
+      <c r="A10" s="126" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B10" s="126" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="11" ht="13.5" customHeight="1">
-      <c r="A11" s="97" t="s">
-        <v>884</v>
-      </c>
-      <c r="B11" s="97" t="s">
-        <v>885</v>
+      <c r="A11" s="126" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B11" s="126" t="s">
+        <v>1039</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1">
-      <c r="A12" s="97" t="s">
-        <v>886</v>
-      </c>
-      <c r="B12" s="97" t="s">
-        <v>887</v>
+      <c r="A12" s="126" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B12" s="126" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="13" ht="6.0" customHeight="1"/>
     <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="95" t="s">
-        <v>888</v>
-      </c>
-      <c r="B14" s="96"/>
+      <c r="A14" s="124" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B14" s="125"/>
     </row>
     <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="97" t="s">
-        <v>889</v>
-      </c>
-      <c r="B15" s="97" t="s">
-        <v>890</v>
+      <c r="A15" s="126" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B15" s="126" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1">
-      <c r="A16" s="97" t="s">
-        <v>891</v>
-      </c>
-      <c r="B16" s="97" t="s">
-        <v>892</v>
+      <c r="A16" s="126" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B16" s="126" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="17" ht="13.5" customHeight="1">
-      <c r="A17" s="97" t="s">
-        <v>893</v>
-      </c>
-      <c r="B17" s="97" t="s">
-        <v>894</v>
+      <c r="A17" s="126" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B17" s="126" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="18" ht="13.5" customHeight="1">
-      <c r="A18" s="97" t="s">
-        <v>895</v>
-      </c>
-      <c r="B18" s="97" t="s">
-        <v>896</v>
+      <c r="A18" s="126" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B18" s="126" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="19" ht="6.0" customHeight="1"/>
     <row r="20" ht="13.5" customHeight="1">
-      <c r="A20" s="95" t="s">
-        <v>897</v>
-      </c>
-      <c r="B20" s="96"/>
+      <c r="A20" s="124" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B20" s="125"/>
     </row>
     <row r="21" ht="13.5" customHeight="1">
-      <c r="A21" s="97" t="s">
-        <v>898</v>
-      </c>
-      <c r="B21" s="97" t="s">
-        <v>899</v>
+      <c r="A21" s="126" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B21" s="126" t="s">
+        <v>1053</v>
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1">
-      <c r="A22" s="97" t="s">
-        <v>900</v>
-      </c>
-      <c r="B22" s="97" t="s">
-        <v>901</v>
+      <c r="A22" s="126" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B22" s="126" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1">
-      <c r="A23" s="98" t="s">
-        <v>902</v>
-      </c>
-      <c r="B23" s="97" t="s">
-        <v>903</v>
+      <c r="A23" s="127" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B23" s="126" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="97" t="s">
-        <v>904</v>
-      </c>
-      <c r="B24" s="97" t="s">
-        <v>905</v>
+      <c r="A24" s="126" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B24" s="126" t="s">
+        <v>1059</v>
       </c>
     </row>
     <row r="25" ht="6.0" customHeight="1"/>
     <row r="26" ht="13.5" customHeight="1">
-      <c r="A26" s="95" t="s">
-        <v>906</v>
-      </c>
-      <c r="B26" s="96"/>
+      <c r="A26" s="124" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B26" s="125"/>
     </row>
     <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="97" t="s">
-        <v>907</v>
-      </c>
-      <c r="B27" s="97" t="s">
-        <v>908</v>
+      <c r="A27" s="126" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B27" s="126" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="97" t="s">
-        <v>909</v>
-      </c>
-      <c r="B28" s="97" t="s">
-        <v>910</v>
+      <c r="A28" s="126" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B28" s="126" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="29" ht="13.5" customHeight="1">
-      <c r="A29" s="97" t="s">
-        <v>911</v>
-      </c>
-      <c r="B29" s="97" t="s">
-        <v>912</v>
+      <c r="A29" s="126" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B29" s="126" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="30" ht="6.0" customHeight="1"/>
     <row r="31" ht="13.5" customHeight="1">
-      <c r="A31" s="95" t="s">
-        <v>913</v>
-      </c>
-      <c r="B31" s="96"/>
+      <c r="A31" s="124" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B31" s="125"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
-      <c r="A32" s="98" t="s">
-        <v>914</v>
-      </c>
-      <c r="B32" s="98" t="s">
-        <v>915</v>
+      <c r="A32" s="127" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B32" s="127" t="s">
+        <v>1069</v>
       </c>
     </row>
     <row r="33" ht="6.0" customHeight="1"/>
     <row r="34" ht="13.5" customHeight="1">
-      <c r="A34" s="95" t="s">
-        <v>916</v>
-      </c>
-      <c r="B34" s="96"/>
+      <c r="A34" s="124" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B34" s="125"/>
     </row>
     <row r="35" ht="13.5" customHeight="1">
-      <c r="A35" s="97" t="s">
-        <v>917</v>
-      </c>
-      <c r="B35" s="97" t="s">
-        <v>918</v>
+      <c r="A35" s="126" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B35" s="126" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="36" ht="6.0" customHeight="1"/>
@@ -13786,57 +15893,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="99" t="s">
-        <v>919</v>
-      </c>
-      <c r="B1" s="99" t="s">
-        <v>920</v>
-      </c>
-      <c r="C1" s="99" t="s">
-        <v>921</v>
+      <c r="A1" s="128" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1" s="128" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>1075</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="100" t="s">
-        <v>922</v>
-      </c>
-      <c r="B2" s="100" t="s">
-        <v>923</v>
-      </c>
-      <c r="C2" s="100" t="b">
+      <c r="A2" s="129" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B2" s="129" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C2" s="129" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="100" t="s">
-        <v>924</v>
-      </c>
-      <c r="B3" s="100" t="s">
-        <v>925</v>
-      </c>
-      <c r="C3" s="100" t="b">
+      <c r="A3" s="129" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B3" s="129" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C3" s="129" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="100" t="s">
-        <v>926</v>
-      </c>
-      <c r="B4" s="100" t="s">
-        <v>927</v>
-      </c>
-      <c r="C4" s="100" t="b">
+      <c r="A4" s="129" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B4" s="129" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C4" s="129" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="100" t="s">
-        <v>928</v>
-      </c>
-      <c r="B5" s="100" t="s">
-        <v>929</v>
-      </c>
-      <c r="C5" s="100" t="b">
+      <c r="A5" s="129" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B5" s="129" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C5" s="129" t="b">
         <v>0</v>
       </c>
     </row>
